--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80134DBD-D9BD-4B56-904B-90C521972077}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9BB9FD-14A3-44E3-A3A2-3A9C4CCB2999}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3920" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="602">
   <si>
     <t>Подразделение</t>
   </si>
@@ -2802,7 +2802,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2812,21 +2827,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3176,7 +3176,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="128" t="s">
         <v>442</v>
       </c>
       <c r="B1" s="125"/>
@@ -3194,64 +3194,64 @@
       <c r="N1" s="125"/>
       <c r="O1" s="125"/>
       <c r="P1" s="125"/>
-      <c r="Q1" s="131"/>
+      <c r="Q1" s="126"/>
       <c r="R1" s="124" t="s">
         <v>231</v>
       </c>
       <c r="S1" s="125"/>
       <c r="T1" s="125"/>
-      <c r="U1" s="131"/>
+      <c r="U1" s="126"/>
       <c r="V1" s="124" t="s">
         <v>232</v>
       </c>
       <c r="W1" s="125"/>
       <c r="X1" s="125"/>
-      <c r="Y1" s="126"/>
-      <c r="Z1" s="126"/>
-      <c r="AA1" s="131"/>
-      <c r="AB1" s="133" t="s">
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="129" t="s">
         <v>233</v>
       </c>
       <c r="AC1" s="130"/>
-      <c r="AD1" s="134"/>
+      <c r="AD1" s="131"/>
       <c r="AE1" s="56" t="s">
         <v>234</v>
       </c>
       <c r="AF1" s="124" t="s">
         <v>235</v>
       </c>
-      <c r="AG1" s="131"/>
+      <c r="AG1" s="126"/>
       <c r="AH1" s="124" t="s">
         <v>236</v>
       </c>
       <c r="AI1" s="130"/>
-      <c r="AJ1" s="131"/>
+      <c r="AJ1" s="126"/>
       <c r="AK1" s="124" t="s">
         <v>237</v>
       </c>
-      <c r="AL1" s="131"/>
+      <c r="AL1" s="126"/>
       <c r="AM1" s="124" t="s">
         <v>238</v>
       </c>
       <c r="AN1" s="125"/>
-      <c r="AO1" s="131"/>
+      <c r="AO1" s="126"/>
       <c r="AP1" s="71" t="s">
         <v>239</v>
       </c>
       <c r="AQ1" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="AR1" s="132" t="s">
+      <c r="AR1" s="128" t="s">
         <v>241</v>
       </c>
-      <c r="AS1" s="131"/>
+      <c r="AS1" s="126"/>
       <c r="AT1" s="124" t="s">
         <v>242</v>
       </c>
       <c r="AU1" s="124"/>
       <c r="AV1" s="125"/>
-      <c r="AW1" s="126"/>
-      <c r="AX1" s="132" t="s">
+      <c r="AW1" s="127"/>
+      <c r="AX1" s="128" t="s">
         <v>408</v>
       </c>
       <c r="AY1" s="124"/>
@@ -3260,15 +3260,15 @@
       <c r="BB1" s="125"/>
       <c r="BC1" s="125"/>
       <c r="BD1" s="125"/>
-      <c r="BE1" s="131"/>
-      <c r="BF1" s="127" t="s">
+      <c r="BE1" s="126"/>
+      <c r="BF1" s="132" t="s">
         <v>243</v>
       </c>
-      <c r="BG1" s="128"/>
-      <c r="BH1" s="128"/>
-      <c r="BI1" s="128"/>
-      <c r="BJ1" s="128"/>
-      <c r="BK1" s="129"/>
+      <c r="BG1" s="133"/>
+      <c r="BH1" s="133"/>
+      <c r="BI1" s="133"/>
+      <c r="BJ1" s="133"/>
+      <c r="BK1" s="134"/>
       <c r="BL1" s="12"/>
     </row>
     <row r="2" spans="1:64" ht="61.8" thickBot="1">
@@ -6989,7 +6989,7 @@
         <v>97</v>
       </c>
       <c r="AG21" s="31">
-        <v>23.5</v>
+        <v>10</v>
       </c>
       <c r="AH21" s="28" t="s">
         <v>97</v>
@@ -7753,35 +7753,35 @@
       <c r="AE25" s="93">
         <v>7</v>
       </c>
-      <c r="AF25" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG25" s="31">
-        <v>43</v>
+      <c r="AF25" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG25" s="59" t="s">
+        <v>24</v>
       </c>
       <c r="AH25" s="28" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="AI25" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ25" s="26">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="AJ25" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="AK25" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL25" s="25">
-        <v>33</v>
+        <v>24</v>
+      </c>
+      <c r="AL25" s="66" t="s">
+        <v>24</v>
       </c>
       <c r="AM25" s="70" t="s">
-        <v>97</v>
-      </c>
-      <c r="AN25" s="16">
-        <v>17</v>
-      </c>
-      <c r="AO25" s="24" t="s">
-        <v>96</v>
+        <v>24</v>
+      </c>
+      <c r="AN25" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO25" s="70" t="s">
+        <v>24</v>
       </c>
       <c r="AP25" s="55" t="s">
         <v>124</v>
@@ -7947,7 +7947,7 @@
         <v>97</v>
       </c>
       <c r="AG26" s="31">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AH26" s="28" t="s">
         <v>97</v>
@@ -8899,7 +8899,7 @@
         <v>97</v>
       </c>
       <c r="AG31" s="31">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AH31" s="28" t="s">
         <v>97</v>
@@ -14988,13 +14988,13 @@
         <v>24</v>
       </c>
       <c r="AH63" s="28" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="AI63" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ63" s="26">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="AJ63" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="AK63" s="66" t="s">
         <v>24</v>
@@ -15003,13 +15003,13 @@
         <v>24</v>
       </c>
       <c r="AM63" s="70" t="s">
-        <v>97</v>
-      </c>
-      <c r="AN63" s="16">
-        <v>4</v>
+        <v>24</v>
+      </c>
+      <c r="AN63" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="AO63" s="24" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="AP63" s="55" t="s">
         <v>24</v>
@@ -18384,11 +18384,6 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="AB1:AD1"/>
     <mergeCell ref="AT1:AW1"/>
     <mergeCell ref="BF1:BK1"/>
     <mergeCell ref="AH1:AJ1"/>
@@ -18396,6 +18391,11 @@
     <mergeCell ref="AM1:AO1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AX1:BE1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="AB1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="U4 BJ4 BI5 BK6 BJ7 U8 BG8 T9 BF9 BI10:BI14 U14 BK15 U17 BF19 BI20 BJ21 U22 BI22 BF23 BG24 U24:U25 BK25 BI26:BI27 BJ28 BG29 U29:U30 BF30 U33 BH33 BI34:BI36 U35 T36 U37 BJ37 U39 BK41 BK52 BI53:BI55 T56 BK56 U57 U61 BG61 U70 U72 T76 BH76 BF77:BF78 BI16:BI18 BI63:BI75 BI57:BI60 BI38:BI40 BG79 BI42:BI51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9BB9FD-14A3-44E3-A3A2-3A9C4CCB2999}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F3E5AF-A534-4BEA-AD19-99F8707BFDCB}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3930" uniqueCount="604">
   <si>
     <t>Подразделение</t>
   </si>
@@ -1834,6 +1834,12 @@
   </si>
   <si>
     <t>1-2</t>
+  </si>
+  <si>
+    <t>спорт</t>
+  </si>
+  <si>
+    <t>29,7*42</t>
   </si>
 </sst>
 </file>
@@ -2429,7 +2435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2664,9 +2670,6 @@
     <xf numFmtId="49" fontId="10" fillId="9" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2693,9 +2696,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="9" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2802,22 +2802,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2827,6 +2812,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3176,151 +3176,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="130" t="s">
         <v>442</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="124" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="122" t="s">
         <v>231</v>
       </c>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="126"/>
-      <c r="V1" s="124" t="s">
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="122" t="s">
         <v>232</v>
       </c>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="127"/>
-      <c r="Z1" s="127"/>
-      <c r="AA1" s="126"/>
-      <c r="AB1" s="129" t="s">
+      <c r="W1" s="123"/>
+      <c r="X1" s="123"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="129"/>
+      <c r="AB1" s="131" t="s">
         <v>233</v>
       </c>
-      <c r="AC1" s="130"/>
-      <c r="AD1" s="131"/>
+      <c r="AC1" s="128"/>
+      <c r="AD1" s="132"/>
       <c r="AE1" s="56" t="s">
         <v>234</v>
       </c>
-      <c r="AF1" s="124" t="s">
+      <c r="AF1" s="122" t="s">
         <v>235</v>
       </c>
-      <c r="AG1" s="126"/>
-      <c r="AH1" s="124" t="s">
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="122" t="s">
         <v>236</v>
       </c>
-      <c r="AI1" s="130"/>
-      <c r="AJ1" s="126"/>
-      <c r="AK1" s="124" t="s">
+      <c r="AI1" s="128"/>
+      <c r="AJ1" s="129"/>
+      <c r="AK1" s="122" t="s">
         <v>237</v>
       </c>
-      <c r="AL1" s="126"/>
-      <c r="AM1" s="124" t="s">
+      <c r="AL1" s="129"/>
+      <c r="AM1" s="122" t="s">
         <v>238</v>
       </c>
-      <c r="AN1" s="125"/>
-      <c r="AO1" s="126"/>
+      <c r="AN1" s="123"/>
+      <c r="AO1" s="129"/>
       <c r="AP1" s="71" t="s">
         <v>239</v>
       </c>
       <c r="AQ1" s="53" t="s">
         <v>240</v>
       </c>
-      <c r="AR1" s="128" t="s">
+      <c r="AR1" s="130" t="s">
         <v>241</v>
       </c>
-      <c r="AS1" s="126"/>
-      <c r="AT1" s="124" t="s">
+      <c r="AS1" s="129"/>
+      <c r="AT1" s="122" t="s">
         <v>242</v>
       </c>
-      <c r="AU1" s="124"/>
-      <c r="AV1" s="125"/>
-      <c r="AW1" s="127"/>
-      <c r="AX1" s="128" t="s">
+      <c r="AU1" s="122"/>
+      <c r="AV1" s="123"/>
+      <c r="AW1" s="124"/>
+      <c r="AX1" s="130" t="s">
         <v>408</v>
       </c>
-      <c r="AY1" s="124"/>
-      <c r="AZ1" s="124"/>
-      <c r="BA1" s="124"/>
-      <c r="BB1" s="125"/>
-      <c r="BC1" s="125"/>
-      <c r="BD1" s="125"/>
-      <c r="BE1" s="126"/>
-      <c r="BF1" s="132" t="s">
+      <c r="AY1" s="122"/>
+      <c r="AZ1" s="122"/>
+      <c r="BA1" s="122"/>
+      <c r="BB1" s="123"/>
+      <c r="BC1" s="123"/>
+      <c r="BD1" s="123"/>
+      <c r="BE1" s="129"/>
+      <c r="BF1" s="125" t="s">
         <v>243</v>
       </c>
-      <c r="BG1" s="133"/>
-      <c r="BH1" s="133"/>
-      <c r="BI1" s="133"/>
-      <c r="BJ1" s="133"/>
-      <c r="BK1" s="134"/>
+      <c r="BG1" s="126"/>
+      <c r="BH1" s="126"/>
+      <c r="BI1" s="126"/>
+      <c r="BJ1" s="126"/>
+      <c r="BK1" s="127"/>
       <c r="BL1" s="12"/>
     </row>
     <row r="2" spans="1:64" ht="61.8" thickBot="1">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>310</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="86" t="s">
         <v>214</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="87" t="s">
+      <c r="E2" s="86" t="s">
         <v>455</v>
       </c>
-      <c r="F2" s="87" t="s">
+      <c r="F2" s="86" t="s">
         <v>456</v>
       </c>
-      <c r="G2" s="87" t="s">
+      <c r="G2" s="86" t="s">
         <v>599</v>
       </c>
-      <c r="H2" s="87" t="s">
+      <c r="H2" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="87" t="s">
+      <c r="J2" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="87" t="s">
+      <c r="K2" s="86" t="s">
         <v>417</v>
       </c>
-      <c r="L2" s="87" t="s">
+      <c r="L2" s="86" t="s">
         <v>440</v>
       </c>
-      <c r="M2" s="87" t="s">
+      <c r="M2" s="86" t="s">
         <v>226</v>
       </c>
-      <c r="N2" s="87" t="s">
+      <c r="N2" s="86" t="s">
         <v>227</v>
       </c>
-      <c r="O2" s="87" t="s">
+      <c r="O2" s="86" t="s">
         <v>288</v>
       </c>
-      <c r="P2" s="87" t="s">
+      <c r="P2" s="86" t="s">
         <v>443</v>
       </c>
-      <c r="Q2" s="88" t="s">
+      <c r="Q2" s="87" t="s">
         <v>444</v>
       </c>
       <c r="R2" s="41" t="s">
@@ -3350,19 +3350,19 @@
       <c r="Z2" s="79" t="s">
         <v>412</v>
       </c>
-      <c r="AA2" s="89" t="s">
+      <c r="AA2" s="88" t="s">
         <v>413</v>
       </c>
       <c r="AB2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="91" t="s">
+      <c r="AC2" s="89" t="s">
         <v>8</v>
       </c>
       <c r="AD2" s="47" t="s">
         <v>594</v>
       </c>
-      <c r="AE2" s="92" t="s">
+      <c r="AE2" s="90" t="s">
         <v>9</v>
       </c>
       <c r="AF2" s="57" t="s">
@@ -3371,7 +3371,7 @@
       <c r="AG2" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="AH2" s="95" t="s">
+      <c r="AH2" s="93" t="s">
         <v>12</v>
       </c>
       <c r="AI2" s="61" t="s">
@@ -3404,7 +3404,7 @@
       <c r="AR2" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AS2" s="83" t="s">
+      <c r="AS2" s="82" t="s">
         <v>20</v>
       </c>
       <c r="AT2" s="50" t="s">
@@ -3416,10 +3416,10 @@
       <c r="AV2" s="51" t="s">
         <v>422</v>
       </c>
-      <c r="AW2" s="85" t="s">
+      <c r="AW2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="AX2" s="84" t="s">
+      <c r="AX2" s="83" t="s">
         <v>22</v>
       </c>
       <c r="AY2" s="48" t="s">
@@ -3526,22 +3526,22 @@
         <v>24</v>
       </c>
       <c r="V3" s="80" t="s">
-        <v>97</v>
-      </c>
-      <c r="W3" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="X3" s="81" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y3" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z3" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="90">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="W3" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="X3" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y3" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="80" t="s">
+        <v>24</v>
       </c>
       <c r="AB3" s="7">
         <v>7</v>
@@ -3552,7 +3552,7 @@
       <c r="AD3" s="8">
         <v>3.6</v>
       </c>
-      <c r="AE3" s="93">
+      <c r="AE3" s="91">
         <v>6</v>
       </c>
       <c r="AF3" s="59" t="s">
@@ -3580,7 +3580,7 @@
         <v>97</v>
       </c>
       <c r="AN3" s="16">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AO3" s="24" t="s">
         <v>96</v>
@@ -3594,7 +3594,7 @@
       <c r="AR3" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="AS3" s="82" t="s">
+      <c r="AS3" s="81" t="s">
         <v>97</v>
       </c>
       <c r="AT3" s="7" t="s">
@@ -3707,7 +3707,7 @@
         <v>24</v>
       </c>
       <c r="S4" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>24</v>
@@ -3742,44 +3742,44 @@
       <c r="AD4" s="8">
         <v>5.76</v>
       </c>
-      <c r="AE4" s="93">
+      <c r="AE4" s="91">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG4" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH4" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI4" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ4" s="26">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL4" s="25">
+        <v>16</v>
+      </c>
+      <c r="AM4" s="70" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN4" s="16">
         <v>9</v>
-      </c>
-      <c r="AF4" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG4" s="31">
-        <v>44.5</v>
-      </c>
-      <c r="AH4" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI4" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ4" s="26">
-        <v>4</v>
-      </c>
-      <c r="AK4" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL4" s="25">
-        <v>18</v>
-      </c>
-      <c r="AM4" s="70" t="s">
-        <v>97</v>
-      </c>
-      <c r="AN4" s="16">
-        <v>7</v>
       </c>
       <c r="AO4" s="24" t="s">
         <v>96</v>
       </c>
       <c r="AP4" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="AQ4" s="55">
-        <v>1</v>
+        <v>602</v>
+      </c>
+      <c r="AQ4" s="55" t="s">
+        <v>24</v>
       </c>
       <c r="AR4" s="7" t="s">
         <v>109</v>
@@ -3811,8 +3811,8 @@
       <c r="BA4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="BB4" s="2">
-        <v>2</v>
+      <c r="BB4" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="BC4" s="2" t="s">
         <v>24</v>
@@ -3920,7 +3920,7 @@
       <c r="Z5" s="4">
         <v>3</v>
       </c>
-      <c r="AA5" s="82">
+      <c r="AA5" s="81">
         <v>2</v>
       </c>
       <c r="AB5" s="23">
@@ -3932,7 +3932,7 @@
       <c r="AD5" s="9">
         <v>7.2</v>
       </c>
-      <c r="AE5" s="94">
+      <c r="AE5" s="92">
         <v>6</v>
       </c>
       <c r="AF5" s="59" t="s">
@@ -3974,7 +3974,7 @@
       <c r="AR5" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="AS5" s="82" t="s">
+      <c r="AS5" s="81" t="s">
         <v>97</v>
       </c>
       <c r="AT5" s="23" t="s">
@@ -4122,7 +4122,7 @@
       <c r="AD6" s="8">
         <v>4.3</v>
       </c>
-      <c r="AE6" s="93">
+      <c r="AE6" s="91">
         <v>8</v>
       </c>
       <c r="AF6" s="59" t="s">
@@ -4312,7 +4312,7 @@
       <c r="AD7" s="8">
         <v>2.6</v>
       </c>
-      <c r="AE7" s="93">
+      <c r="AE7" s="91">
         <v>5</v>
       </c>
       <c r="AF7" s="60" t="s">
@@ -4504,7 +4504,7 @@
       <c r="AD8" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE8" s="93">
+      <c r="AE8" s="91">
         <v>7</v>
       </c>
       <c r="AF8" s="60" t="s">
@@ -4696,7 +4696,7 @@
       <c r="AD9" s="8">
         <v>6.5</v>
       </c>
-      <c r="AE9" s="93">
+      <c r="AE9" s="91">
         <v>10</v>
       </c>
       <c r="AF9" s="60" t="s">
@@ -4886,7 +4886,7 @@
       <c r="AD10" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE10" s="93">
+      <c r="AE10" s="91">
         <v>2</v>
       </c>
       <c r="AF10" s="59" t="s">
@@ -5078,14 +5078,14 @@
       <c r="AD11" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE11" s="93">
+      <c r="AE11" s="91">
         <v>3</v>
       </c>
       <c r="AF11" s="60" t="s">
         <v>97</v>
       </c>
       <c r="AG11" s="31">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AH11" s="28" t="s">
         <v>97</v>
@@ -5100,7 +5100,7 @@
         <v>97</v>
       </c>
       <c r="AL11" s="25">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AM11" s="70" t="s">
         <v>97</v>
@@ -5268,7 +5268,7 @@
       <c r="AD12" s="8">
         <v>3.24</v>
       </c>
-      <c r="AE12" s="93">
+      <c r="AE12" s="91">
         <v>5</v>
       </c>
       <c r="AF12" s="59" t="s">
@@ -5458,7 +5458,7 @@
       <c r="AD13" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE13" s="93">
+      <c r="AE13" s="91">
         <v>2</v>
       </c>
       <c r="AF13" s="59" t="s">
@@ -5650,7 +5650,7 @@
       <c r="AD14" s="8">
         <v>7.02</v>
       </c>
-      <c r="AE14" s="93">
+      <c r="AE14" s="91">
         <v>3</v>
       </c>
       <c r="AF14" s="59" t="s">
@@ -5840,7 +5840,7 @@
       <c r="AD15" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE15" s="93">
+      <c r="AE15" s="91">
         <v>8</v>
       </c>
       <c r="AF15" s="59" t="s">
@@ -6030,7 +6030,7 @@
       <c r="AD16" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE16" s="93">
+      <c r="AE16" s="91">
         <v>4</v>
       </c>
       <c r="AF16" s="60" t="s">
@@ -6222,7 +6222,7 @@
       <c r="AD17" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE17" s="93">
+      <c r="AE17" s="91">
         <v>8</v>
       </c>
       <c r="AF17" s="59" t="s">
@@ -6412,7 +6412,7 @@
       <c r="AD18" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE18" s="93">
+      <c r="AE18" s="91">
         <v>2</v>
       </c>
       <c r="AF18" s="59" t="s">
@@ -6602,7 +6602,7 @@
       <c r="AD19" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE19" s="93">
+      <c r="AE19" s="91">
         <v>4</v>
       </c>
       <c r="AF19" s="59" t="s">
@@ -6792,7 +6792,7 @@
       <c r="AD20" s="8">
         <v>5.4</v>
       </c>
-      <c r="AE20" s="93">
+      <c r="AE20" s="91">
         <v>7</v>
       </c>
       <c r="AF20" s="59" t="s">
@@ -6982,7 +6982,7 @@
       <c r="AD21" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE21" s="93">
+      <c r="AE21" s="91">
         <v>5</v>
       </c>
       <c r="AF21" s="60" t="s">
@@ -7174,7 +7174,7 @@
       <c r="AD22" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE22" s="93">
+      <c r="AE22" s="91">
         <v>5</v>
       </c>
       <c r="AF22" s="60" t="s">
@@ -7366,7 +7366,7 @@
       <c r="AD23" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE23" s="93">
+      <c r="AE23" s="91">
         <v>14</v>
       </c>
       <c r="AF23" s="60" t="s">
@@ -7558,7 +7558,7 @@
       <c r="AD24" s="8">
         <v>7</v>
       </c>
-      <c r="AE24" s="93">
+      <c r="AE24" s="91">
         <v>12</v>
       </c>
       <c r="AF24" s="60" t="s">
@@ -7750,7 +7750,7 @@
       <c r="AD25" s="8">
         <v>7.56</v>
       </c>
-      <c r="AE25" s="93">
+      <c r="AE25" s="91">
         <v>7</v>
       </c>
       <c r="AF25" s="59" t="s">
@@ -7940,7 +7940,7 @@
       <c r="AD26" s="8">
         <v>3.24</v>
       </c>
-      <c r="AE26" s="93">
+      <c r="AE26" s="91">
         <v>2</v>
       </c>
       <c r="AF26" s="60" t="s">
@@ -8130,7 +8130,7 @@
       <c r="AD27" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE27" s="93">
+      <c r="AE27" s="91">
         <v>2</v>
       </c>
       <c r="AF27" s="59" t="s">
@@ -8320,7 +8320,7 @@
       <c r="AD28" s="8">
         <v>7.02</v>
       </c>
-      <c r="AE28" s="93">
+      <c r="AE28" s="91">
         <v>5</v>
       </c>
       <c r="AF28" s="59" t="s">
@@ -8512,7 +8512,7 @@
       <c r="AD29" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE29" s="93">
+      <c r="AE29" s="91">
         <v>14</v>
       </c>
       <c r="AF29" s="60" t="s">
@@ -8702,7 +8702,7 @@
       <c r="AD30" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE30" s="93">
+      <c r="AE30" s="91">
         <v>2</v>
       </c>
       <c r="AF30" s="60" t="s">
@@ -8892,7 +8892,7 @@
       <c r="AD31" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE31" s="93">
+      <c r="AE31" s="91">
         <v>2</v>
       </c>
       <c r="AF31" s="60" t="s">
@@ -9082,7 +9082,7 @@
       <c r="AD32" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE32" s="93">
+      <c r="AE32" s="91">
         <v>3</v>
       </c>
       <c r="AF32" s="59" t="s">
@@ -9274,7 +9274,7 @@
       <c r="AD33" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE33" s="93">
+      <c r="AE33" s="91">
         <v>10</v>
       </c>
       <c r="AF33" s="60" t="s">
@@ -9464,7 +9464,7 @@
       <c r="AD34" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE34" s="93">
+      <c r="AE34" s="91">
         <v>3</v>
       </c>
       <c r="AF34" s="60" t="s">
@@ -9654,7 +9654,7 @@
       <c r="AD35" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE35" s="93">
+      <c r="AE35" s="91">
         <v>5</v>
       </c>
       <c r="AF35" s="60" t="s">
@@ -9844,7 +9844,7 @@
       <c r="AD36" s="8">
         <v>2.16</v>
       </c>
-      <c r="AE36" s="93">
+      <c r="AE36" s="91">
         <v>2</v>
       </c>
       <c r="AF36" s="59" t="s">
@@ -10034,7 +10034,7 @@
       <c r="AD37" s="8">
         <v>10.26</v>
       </c>
-      <c r="AE37" s="93">
+      <c r="AE37" s="91">
         <v>7</v>
       </c>
       <c r="AF37" s="60" t="s">
@@ -10224,7 +10224,7 @@
       <c r="AD38" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE38" s="93">
+      <c r="AE38" s="91">
         <v>4</v>
       </c>
       <c r="AF38" s="59" t="s">
@@ -10414,7 +10414,7 @@
       <c r="AD39" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE39" s="93">
+      <c r="AE39" s="91">
         <v>4</v>
       </c>
       <c r="AF39" s="59" t="s">
@@ -10604,7 +10604,7 @@
       <c r="AD40" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE40" s="93">
+      <c r="AE40" s="91">
         <v>2</v>
       </c>
       <c r="AF40" s="59" t="s">
@@ -10794,7 +10794,7 @@
       <c r="AD41" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE41" s="93">
+      <c r="AE41" s="91">
         <v>2</v>
       </c>
       <c r="AF41" s="60" t="s">
@@ -10984,7 +10984,7 @@
       <c r="AD42" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE42" s="93">
+      <c r="AE42" s="91">
         <v>2</v>
       </c>
       <c r="AF42" s="59" t="s">
@@ -11174,7 +11174,7 @@
       <c r="AD43" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE43" s="93">
+      <c r="AE43" s="91">
         <v>2</v>
       </c>
       <c r="AF43" s="59" t="s">
@@ -11364,7 +11364,7 @@
       <c r="AD44" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE44" s="93">
+      <c r="AE44" s="91">
         <v>3</v>
       </c>
       <c r="AF44" s="60" t="s">
@@ -11554,7 +11554,7 @@
       <c r="AD45" s="8">
         <v>5.4</v>
       </c>
-      <c r="AE45" s="93">
+      <c r="AE45" s="91">
         <v>8</v>
       </c>
       <c r="AF45" s="59" t="s">
@@ -11744,7 +11744,7 @@
       <c r="AD46" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE46" s="93">
+      <c r="AE46" s="91">
         <v>8</v>
       </c>
       <c r="AF46" s="59" t="s">
@@ -11934,7 +11934,7 @@
       <c r="AD47" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE47" s="93">
+      <c r="AE47" s="91">
         <v>3</v>
       </c>
       <c r="AF47" s="59" t="s">
@@ -12124,7 +12124,7 @@
       <c r="AD48" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE48" s="93">
+      <c r="AE48" s="91">
         <v>4</v>
       </c>
       <c r="AF48" s="60" t="s">
@@ -12314,7 +12314,7 @@
       <c r="AD49" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE49" s="93">
+      <c r="AE49" s="91">
         <v>11</v>
       </c>
       <c r="AF49" s="59" t="s">
@@ -12504,7 +12504,7 @@
       <c r="AD50" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE50" s="93">
+      <c r="AE50" s="91">
         <v>3</v>
       </c>
       <c r="AF50" s="59" t="s">
@@ -12514,13 +12514,13 @@
         <v>24</v>
       </c>
       <c r="AH50" s="28" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="AI50" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ50" s="26">
-        <v>1.5</v>
+        <v>24</v>
+      </c>
+      <c r="AJ50" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="AK50" s="66" t="s">
         <v>24</v>
@@ -12694,7 +12694,7 @@
       <c r="AD51" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE51" s="93">
+      <c r="AE51" s="91">
         <v>10</v>
       </c>
       <c r="AF51" s="60" t="s">
@@ -12884,7 +12884,7 @@
       <c r="AD52" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE52" s="93">
+      <c r="AE52" s="91">
         <v>4</v>
       </c>
       <c r="AF52" s="60" t="s">
@@ -13074,7 +13074,7 @@
       <c r="AD53" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE53" s="93">
+      <c r="AE53" s="91">
         <v>5</v>
       </c>
       <c r="AF53" s="60" t="s">
@@ -13264,7 +13264,7 @@
       <c r="AD54" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE54" s="93">
+      <c r="AE54" s="91">
         <v>4</v>
       </c>
       <c r="AF54" s="59" t="s">
@@ -13454,7 +13454,7 @@
       <c r="AD55" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE55" s="93">
+      <c r="AE55" s="91">
         <v>2</v>
       </c>
       <c r="AF55" s="60" t="s">
@@ -13646,7 +13646,7 @@
       <c r="AD56" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE56" s="93">
+      <c r="AE56" s="91">
         <v>7</v>
       </c>
       <c r="AF56" s="60" t="s">
@@ -13836,7 +13836,7 @@
       <c r="AD57" s="8">
         <v>11.34</v>
       </c>
-      <c r="AE57" s="93">
+      <c r="AE57" s="91">
         <v>3</v>
       </c>
       <c r="AF57" s="59" t="s">
@@ -14026,7 +14026,7 @@
       <c r="AD58" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE58" s="93">
+      <c r="AE58" s="91">
         <v>3</v>
       </c>
       <c r="AF58" s="59" t="s">
@@ -14216,7 +14216,7 @@
       <c r="AD59" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE59" s="93">
+      <c r="AE59" s="91">
         <v>6</v>
       </c>
       <c r="AF59" s="59" t="s">
@@ -14406,7 +14406,7 @@
       <c r="AD60" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE60" s="93">
+      <c r="AE60" s="91">
         <v>7</v>
       </c>
       <c r="AF60" s="59" t="s">
@@ -14598,7 +14598,7 @@
       <c r="AD61" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE61" s="93">
+      <c r="AE61" s="91">
         <v>10</v>
       </c>
       <c r="AF61" s="60" t="s">
@@ -14788,7 +14788,7 @@
       <c r="AD62" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE62" s="93">
+      <c r="AE62" s="91">
         <v>4</v>
       </c>
       <c r="AF62" s="60" t="s">
@@ -14978,7 +14978,7 @@
       <c r="AD63" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE63" s="93">
+      <c r="AE63" s="91">
         <v>4</v>
       </c>
       <c r="AF63" s="59" t="s">
@@ -15168,7 +15168,7 @@
       <c r="AD64" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE64" s="93">
+      <c r="AE64" s="91">
         <v>5</v>
       </c>
       <c r="AF64" s="59" t="s">
@@ -15358,7 +15358,7 @@
       <c r="AD65" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE65" s="93">
+      <c r="AE65" s="91">
         <v>6</v>
       </c>
       <c r="AF65" s="59" t="s">
@@ -15548,7 +15548,7 @@
       <c r="AD66" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE66" s="93">
+      <c r="AE66" s="91">
         <v>2</v>
       </c>
       <c r="AF66" s="60" t="s">
@@ -15738,7 +15738,7 @@
       <c r="AD67" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE67" s="93">
+      <c r="AE67" s="91">
         <v>4</v>
       </c>
       <c r="AF67" s="60" t="s">
@@ -15928,7 +15928,7 @@
       <c r="AD68" s="8">
         <v>4.32</v>
       </c>
-      <c r="AE68" s="93">
+      <c r="AE68" s="91">
         <v>4</v>
       </c>
       <c r="AF68" s="59" t="s">
@@ -16118,7 +16118,7 @@
       <c r="AD69" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE69" s="93">
+      <c r="AE69" s="91">
         <v>3</v>
       </c>
       <c r="AF69" s="60" t="s">
@@ -16308,14 +16308,14 @@
       <c r="AD70" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE70" s="93">
+      <c r="AE70" s="91">
         <v>4</v>
       </c>
       <c r="AF70" s="60" t="s">
         <v>97</v>
       </c>
       <c r="AG70" s="31">
-        <v>27</v>
+        <v>20.5</v>
       </c>
       <c r="AH70" s="28" t="s">
         <v>97</v>
@@ -16330,13 +16330,13 @@
         <v>97</v>
       </c>
       <c r="AL70" s="25">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM70" s="70" t="s">
         <v>97</v>
       </c>
       <c r="AN70" s="16">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AO70" s="24" t="s">
         <v>92</v>
@@ -16498,7 +16498,7 @@
       <c r="AD71" s="8">
         <v>3.78</v>
       </c>
-      <c r="AE71" s="93">
+      <c r="AE71" s="91">
         <v>7</v>
       </c>
       <c r="AF71" s="60" t="s">
@@ -16690,7 +16690,7 @@
       <c r="AD72" s="8">
         <v>6.48</v>
       </c>
-      <c r="AE72" s="93">
+      <c r="AE72" s="91">
         <v>4</v>
       </c>
       <c r="AF72" s="60" t="s">
@@ -16880,7 +16880,7 @@
       <c r="AD73" s="8">
         <v>5.94</v>
       </c>
-      <c r="AE73" s="93">
+      <c r="AE73" s="91">
         <v>7</v>
       </c>
       <c r="AF73" s="60" t="s">
@@ -17070,7 +17070,7 @@
       <c r="AD74" s="8">
         <v>5.4</v>
       </c>
-      <c r="AE74" s="93">
+      <c r="AE74" s="91">
         <v>4</v>
       </c>
       <c r="AF74" s="60" t="s">
@@ -17260,7 +17260,7 @@
       <c r="AD75" s="8">
         <v>5.4</v>
       </c>
-      <c r="AE75" s="93">
+      <c r="AE75" s="91">
         <v>2</v>
       </c>
       <c r="AF75" s="59" t="s">
@@ -17452,7 +17452,7 @@
       <c r="AD76" s="8">
         <v>9.7200000000000006</v>
       </c>
-      <c r="AE76" s="93">
+      <c r="AE76" s="91">
         <v>11</v>
       </c>
       <c r="AF76" s="60" t="s">
@@ -17642,7 +17642,7 @@
       <c r="AD77" s="8">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE77" s="93">
+      <c r="AE77" s="91">
         <v>5</v>
       </c>
       <c r="AF77" s="59" t="s">
@@ -17832,7 +17832,7 @@
       <c r="AD78" s="8">
         <v>5.4</v>
       </c>
-      <c r="AE78" s="93">
+      <c r="AE78" s="91">
         <v>3</v>
       </c>
       <c r="AF78" s="59" t="s">
@@ -17934,197 +17934,197 @@
       <c r="BL78" s="12"/>
     </row>
     <row r="79" spans="1:64" ht="15.45" customHeight="1">
-      <c r="A79" s="96" t="s">
+      <c r="A79" s="94" t="s">
         <v>311</v>
       </c>
-      <c r="B79" s="97" t="s">
+      <c r="B79" s="95" t="s">
         <v>190</v>
       </c>
-      <c r="C79" s="97" t="s">
+      <c r="C79" s="95" t="s">
         <v>203</v>
       </c>
-      <c r="D79" s="97" t="s">
+      <c r="D79" s="95" t="s">
         <v>212</v>
       </c>
-      <c r="E79" s="98" t="s">
+      <c r="E79" s="96" t="s">
         <v>488</v>
       </c>
-      <c r="F79" s="98" t="s">
+      <c r="F79" s="96" t="s">
         <v>589</v>
       </c>
-      <c r="G79" s="98" t="s">
+      <c r="G79" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="H79" s="97" t="s">
+      <c r="H79" s="95" t="s">
         <v>186</v>
       </c>
-      <c r="I79" s="99" t="s">
+      <c r="I79" s="97" t="s">
         <v>188</v>
       </c>
-      <c r="J79" s="100">
+      <c r="J79" s="98">
         <v>4</v>
       </c>
-      <c r="K79" s="100"/>
-      <c r="L79" s="97">
+      <c r="K79" s="98"/>
+      <c r="L79" s="95">
         <v>1371</v>
       </c>
-      <c r="M79" s="97" t="s">
+      <c r="M79" s="95" t="s">
         <v>405</v>
       </c>
-      <c r="N79" s="97">
+      <c r="N79" s="95">
         <v>698</v>
       </c>
-      <c r="O79" s="100" t="s">
-        <v>24</v>
-      </c>
-      <c r="P79" s="100" t="s">
+      <c r="O79" s="98" t="s">
+        <v>24</v>
+      </c>
+      <c r="P79" s="98" t="s">
         <v>446</v>
       </c>
-      <c r="Q79" s="101" t="s">
+      <c r="Q79" s="99" t="s">
         <v>448</v>
       </c>
-      <c r="R79" s="102" t="s">
-        <v>24</v>
-      </c>
-      <c r="S79" s="103">
+      <c r="R79" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="S79" s="101">
         <v>20</v>
       </c>
-      <c r="T79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="U79" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="V79" s="105" t="s">
-        <v>24</v>
-      </c>
-      <c r="W79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="X79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA79" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB79" s="105">
+      <c r="T79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="U79" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="V79" s="103" t="s">
+        <v>24</v>
+      </c>
+      <c r="W79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="X79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA79" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB79" s="103">
         <v>9</v>
       </c>
-      <c r="AC79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD79" s="106">
+      <c r="AC79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD79" s="104">
         <v>4.8600000000000003</v>
       </c>
-      <c r="AE79" s="107">
+      <c r="AE79" s="105">
         <v>3</v>
       </c>
-      <c r="AF79" s="108" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG79" s="109" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH79" s="110" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI79" s="110" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ79" s="111" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK79" s="112" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL79" s="113">
+      <c r="AF79" s="106" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG79" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH79" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI79" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ79" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK79" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="AL79" s="111">
         <v>28</v>
       </c>
-      <c r="AM79" s="114" t="s">
-        <v>97</v>
-      </c>
-      <c r="AN79" s="115">
+      <c r="AM79" s="112" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN79" s="113">
         <v>6.5</v>
       </c>
-      <c r="AO79" s="116" t="s">
+      <c r="AO79" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="AP79" s="117" t="s">
-        <v>24</v>
-      </c>
-      <c r="AQ79" s="117" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR79" s="118" t="s">
+      <c r="AP79" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="AQ79" s="115" t="s">
+        <v>24</v>
+      </c>
+      <c r="AR79" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="AS79" s="104" t="s">
-        <v>24</v>
-      </c>
-      <c r="AT79" s="105" t="s">
+      <c r="AS79" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT79" s="103" t="s">
         <v>127</v>
       </c>
-      <c r="AU79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="AV79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="AW79" s="119" t="s">
+      <c r="AU79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="AV79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="AW79" s="117" t="s">
         <v>106</v>
       </c>
-      <c r="AX79" s="102" t="s">
-        <v>24</v>
-      </c>
-      <c r="AY79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="AZ79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="BA79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="BB79" s="103">
+      <c r="AX79" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="AY79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="AZ79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="BA79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="BB79" s="101">
         <v>7</v>
       </c>
-      <c r="BC79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="BD79" s="103">
+      <c r="BC79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="BD79" s="101">
         <v>1</v>
       </c>
-      <c r="BE79" s="106" t="s">
-        <v>24</v>
-      </c>
-      <c r="BF79" s="102" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG79" s="120" t="s">
-        <v>97</v>
-      </c>
-      <c r="BH79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="BJ79" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK79" s="106" t="s">
+      <c r="BE79" s="104" t="s">
+        <v>24</v>
+      </c>
+      <c r="BF79" s="100" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG79" s="118" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ79" s="101" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK79" s="104" t="s">
         <v>24</v>
       </c>
       <c r="BL79" s="12"/>
     </row>
     <row r="80" spans="1:64">
-      <c r="A80" s="121" t="s">
+      <c r="A80" s="119" t="s">
         <v>311</v>
       </c>
       <c r="B80" s="36" t="s">
@@ -18173,11 +18173,11 @@
       <c r="Q80" s="39" t="s">
         <v>454</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>24</v>
+      <c r="R80" s="2">
+        <v>6</v>
       </c>
       <c r="S80" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>24</v>
@@ -18215,10 +18215,10 @@
       <c r="AE80" s="2">
         <v>3</v>
       </c>
-      <c r="AF80" s="122" t="s">
-        <v>24</v>
-      </c>
-      <c r="AG80" s="122" t="s">
+      <c r="AF80" s="120" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG80" s="120" t="s">
         <v>24</v>
       </c>
       <c r="AH80" s="14" t="s">
@@ -18251,23 +18251,23 @@
       <c r="AQ80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AR80" s="123" t="s">
+      <c r="AR80" s="121" t="s">
         <v>109</v>
       </c>
       <c r="AS80" s="2" t="s">
         <v>24</v>
       </c>
       <c r="AT80" s="2" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="AU80" s="2" t="s">
-        <v>24</v>
+        <v>603</v>
       </c>
       <c r="AV80" s="2" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="AW80" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="AX80" s="2" t="s">
         <v>24</v>
@@ -18384,6 +18384,11 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="12">
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="AB1:AD1"/>
     <mergeCell ref="AT1:AW1"/>
     <mergeCell ref="BF1:BK1"/>
     <mergeCell ref="AH1:AJ1"/>
@@ -18391,11 +18396,6 @@
     <mergeCell ref="AM1:AO1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AX1:BE1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="AB1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="U4 BJ4 BI5 BK6 BJ7 U8 BG8 T9 BF9 BI10:BI14 U14 BK15 U17 BF19 BI20 BJ21 U22 BI22 BF23 BG24 U24:U25 BK25 BI26:BI27 BJ28 BG29 U29:U30 BF30 U33 BH33 BI34:BI36 U35 T36 U37 BJ37 U39 BK41 BK52 BI53:BI55 T56 BK56 U57 U61 BG61 U70 U72 T76 BH76 BF77:BF78 BI16:BI18 BI63:BI75 BI57:BI60 BI38:BI40 BG79 BI42:BI51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">
@@ -18413,7 +18413,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BK56 BF77:BF78 BF9 BF19 BF23 BF30 BD75:BD79 BG8 BG24 BG29 BG61 BH76 BH33 BI5 BI10:BI14 BI20 BI22 BI26:BI27 BI31:BI32 BI34:BI36 BI53:BI55 BJ4 BJ7 BJ21 BJ28 BJ37 BD72:BD73 BE56 BK62 BK6 BK15 BK25 BK41 BE66 BK52 T76 T9 T36 U4 U8 U14 U17 U22 U24:U25 U29:U30 U33 U35 U37 U39 U57 U61 U70 U72 T56 BB3:BB5 BB51:BB56 BC77:BC78 BC6:BC7 BC9:BC13 BC15:BC16 BB18:BC27 BC29:BC31 BC51:BC54 BC56 BE76 BD14:BD16 BC3:BD3 BE22 BD5:BD7 BE11 BE26 BE33 BE41 BD10:BD12 BD18:BD22 BD24:BD27 BE24 BE29 BE37 BD64:BD67 BB58:BC58 BB7:BB16 BI16:BI18 BD29:BD32 BC33:BD35 BC60:BC65 BI63:BI75 BD51:BD61 BI57:BI60 BI38:BI40 BC37:BC41 BD37:BD44 BG79 BB60:BB80 BC67:BC75 BD69:BD70 BB29:BB49 BD46:BD49 BC43:BC49 BI42:BI51" xr:uid="{A4FFEF95-B930-418D-AC80-C6F1FD5FE0CE}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="BK56 BF77:BF78 BF9 BF19 BF23 BF30 BD75:BD79 BG8 BG24 BG29 BG61 BH76 BH33 BI5 BI10:BI14 BI20 BI22 BI26:BI27 BI31:BI32 BI34:BI36 BI53:BI55 BJ4 BJ7 BJ21 BJ28 BJ37 BD72:BD73 BE56 BK62 BK6 BK15 BK25 BK41 BE66 BK52 T76 T9 T36 U4 U8 U14 U17 U22 U24:U25 U29:U30 U33 U35 U37 U39 U57 U61 U70 U72 T56 BI42:BI51 BB51:BB56 BC77:BC78 BC6:BC7 BC9:BC13 BC15:BC16 BB18:BC27 BC29:BC31 BC51:BC54 BC56 BE76 BD14:BD16 BE22 BD5:BD7 BE11 BE26 BE33 BE41 BD10:BD12 BD18:BD22 BD24:BD27 BE24 BE29 BE37 BD64:BD67 BB58:BC58 BB7:BB16 BI16:BI18 BD29:BD32 BC33:BD35 BC60:BC65 BI63:BI75 BD51:BD61 BI57:BI60 BI38:BI40 BC37:BC41 BD37:BD44 BG79 BB60:BB80 BC67:BC75 BD69:BD70 BB29:BB49 BD46:BD49 BC43:BC49 BB3:BD3 BB5" xr:uid="{A4FFEF95-B930-418D-AC80-C6F1FD5FE0CE}">
       <formula1>"0,1,10,12,14,16,18,2,3,4,5,6,7,8,9,да,нет"</formula1>
     </dataValidation>
   </dataValidations>

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519A90C3-F6F5-492D-8884-3EFDF92BD8A8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D372A0FD-832E-4222-9FD4-7DF1139AB725}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2942,47 +2942,8 @@
     <xf numFmtId="49" fontId="2" fillId="18" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="19" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="17" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3001,6 +2962,45 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3355,107 +3355,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="143" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="126" t="s">
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="126" t="s">
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="138" t="s">
         <v>230</v>
       </c>
-      <c r="W1" s="127"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="129"/>
-      <c r="Z1" s="129"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="131" t="s">
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="142"/>
+      <c r="Z1" s="142"/>
+      <c r="AA1" s="140"/>
+      <c r="AB1" s="144" t="s">
         <v>231</v>
       </c>
-      <c r="AC1" s="132"/>
-      <c r="AD1" s="133"/>
+      <c r="AC1" s="139"/>
+      <c r="AD1" s="145"/>
       <c r="AE1" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="AF1" s="126" t="s">
+      <c r="AF1" s="138" t="s">
         <v>233</v>
       </c>
-      <c r="AG1" s="128"/>
-      <c r="AH1" s="126" t="s">
+      <c r="AG1" s="140"/>
+      <c r="AH1" s="138" t="s">
         <v>234</v>
       </c>
-      <c r="AI1" s="132"/>
-      <c r="AJ1" s="128"/>
-      <c r="AK1" s="126" t="s">
+      <c r="AI1" s="139"/>
+      <c r="AJ1" s="140"/>
+      <c r="AK1" s="138" t="s">
         <v>235</v>
       </c>
-      <c r="AL1" s="128"/>
-      <c r="AM1" s="126" t="s">
+      <c r="AL1" s="140"/>
+      <c r="AM1" s="138" t="s">
         <v>236</v>
       </c>
-      <c r="AN1" s="127"/>
-      <c r="AO1" s="128"/>
+      <c r="AN1" s="141"/>
+      <c r="AO1" s="140"/>
       <c r="AP1" s="65" t="s">
         <v>237</v>
       </c>
       <c r="AQ1" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="AR1" s="137" t="s">
+      <c r="AR1" s="133" t="s">
         <v>239</v>
       </c>
-      <c r="AS1" s="135"/>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="134" t="s">
+      <c r="AS1" s="134"/>
+      <c r="AT1" s="135"/>
+      <c r="AU1" s="136" t="s">
         <v>240</v>
       </c>
-      <c r="AV1" s="135"/>
-      <c r="AW1" s="135"/>
-      <c r="AX1" s="135"/>
-      <c r="AY1" s="136"/>
-      <c r="AZ1" s="126" t="s">
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="134"/>
+      <c r="AX1" s="134"/>
+      <c r="AY1" s="135"/>
+      <c r="AZ1" s="138" t="s">
         <v>406</v>
       </c>
-      <c r="BA1" s="126"/>
-      <c r="BB1" s="126"/>
-      <c r="BC1" s="126"/>
-      <c r="BD1" s="127"/>
-      <c r="BE1" s="127"/>
-      <c r="BF1" s="127"/>
-      <c r="BG1" s="128"/>
-      <c r="BH1" s="134" t="s">
+      <c r="BA1" s="138"/>
+      <c r="BB1" s="138"/>
+      <c r="BC1" s="138"/>
+      <c r="BD1" s="141"/>
+      <c r="BE1" s="141"/>
+      <c r="BF1" s="141"/>
+      <c r="BG1" s="140"/>
+      <c r="BH1" s="136" t="s">
         <v>241</v>
       </c>
-      <c r="BI1" s="135"/>
-      <c r="BJ1" s="135"/>
-      <c r="BK1" s="135"/>
-      <c r="BL1" s="135"/>
-      <c r="BM1" s="139"/>
-      <c r="BN1" s="137" t="s">
+      <c r="BI1" s="134"/>
+      <c r="BJ1" s="134"/>
+      <c r="BK1" s="134"/>
+      <c r="BL1" s="134"/>
+      <c r="BM1" s="137"/>
+      <c r="BN1" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="BO1" s="135"/>
-      <c r="BP1" s="135"/>
-      <c r="BQ1" s="136"/>
+      <c r="BO1" s="134"/>
+      <c r="BP1" s="134"/>
+      <c r="BQ1" s="135"/>
       <c r="BR1" s="11"/>
     </row>
     <row r="2" spans="1:70" ht="61.8" thickBot="1">
@@ -3651,19 +3651,19 @@
       <c r="BL2" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="BM2" s="140" t="s">
+      <c r="BM2" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="BN2" s="142" t="s">
+      <c r="BN2" s="129" t="s">
         <v>608</v>
       </c>
-      <c r="BO2" s="141" t="s">
+      <c r="BO2" s="128" t="s">
         <v>605</v>
       </c>
-      <c r="BP2" s="143" t="s">
+      <c r="BP2" s="130" t="s">
         <v>606</v>
       </c>
-      <c r="BQ2" s="138" t="s">
+      <c r="BQ2" s="126" t="s">
         <v>609</v>
       </c>
       <c r="BR2" s="11"/>
@@ -3861,7 +3861,7 @@
       <c r="BN3" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO3" s="144">
+      <c r="BO3" s="131">
         <v>1</v>
       </c>
       <c r="BP3" s="5"/>
@@ -4061,7 +4061,7 @@
       <c r="BN4" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO4" s="144">
+      <c r="BO4" s="131">
         <v>1</v>
       </c>
       <c r="BP4" s="5"/>
@@ -4261,7 +4261,7 @@
       <c r="BN5" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO5" s="144">
+      <c r="BO5" s="131">
         <v>1</v>
       </c>
       <c r="BP5" s="5"/>
@@ -4461,7 +4461,7 @@
       <c r="BN6" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO6" s="144">
+      <c r="BO6" s="131">
         <v>1</v>
       </c>
       <c r="BP6" s="5"/>
@@ -4661,7 +4661,7 @@
       <c r="BN7" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO7" s="144">
+      <c r="BO7" s="131">
         <v>1</v>
       </c>
       <c r="BP7" s="5"/>
@@ -4863,7 +4863,7 @@
       <c r="BN8" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO8" s="144">
+      <c r="BO8" s="131">
         <v>2</v>
       </c>
       <c r="BP8" s="5"/>
@@ -5065,7 +5065,7 @@
       <c r="BN9" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO9" s="144">
+      <c r="BO9" s="131">
         <v>1</v>
       </c>
       <c r="BP9" s="5"/>
@@ -5265,7 +5265,7 @@
       <c r="BN10" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO10" s="144">
+      <c r="BO10" s="131">
         <v>1</v>
       </c>
       <c r="BP10" s="5"/>
@@ -5467,7 +5467,7 @@
       <c r="BN11" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO11" s="144">
+      <c r="BO11" s="131">
         <v>1</v>
       </c>
       <c r="BP11" s="5"/>
@@ -5669,7 +5669,7 @@
       <c r="BN12" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO12" s="144">
+      <c r="BO12" s="131">
         <v>1</v>
       </c>
       <c r="BP12" s="5"/>
@@ -5869,7 +5869,7 @@
       <c r="BN13" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO13" s="144">
+      <c r="BO13" s="131">
         <v>1</v>
       </c>
       <c r="BP13" s="5"/>
@@ -6071,7 +6071,7 @@
       <c r="BN14" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO14" s="144">
+      <c r="BO14" s="131">
         <v>1</v>
       </c>
       <c r="BP14" s="5"/>
@@ -6271,7 +6271,7 @@
       <c r="BN15" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO15" s="144">
+      <c r="BO15" s="131">
         <v>2</v>
       </c>
       <c r="BP15" s="5"/>
@@ -6471,7 +6471,7 @@
       <c r="BN16" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO16" s="144">
+      <c r="BO16" s="131">
         <v>1</v>
       </c>
       <c r="BP16" s="5"/>
@@ -6673,7 +6673,7 @@
       <c r="BN17" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO17" s="144">
+      <c r="BO17" s="131">
         <v>1</v>
       </c>
       <c r="BP17" s="5"/>
@@ -6873,7 +6873,7 @@
       <c r="BN18" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO18" s="144">
+      <c r="BO18" s="131">
         <v>1</v>
       </c>
       <c r="BP18" s="5"/>
@@ -7073,7 +7073,7 @@
       <c r="BN19" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO19" s="145">
+      <c r="BO19" s="132">
         <v>1</v>
       </c>
       <c r="BP19" s="5"/>
@@ -7273,7 +7273,7 @@
       <c r="BN20" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO20" s="144">
+      <c r="BO20" s="131">
         <v>1</v>
       </c>
       <c r="BP20" s="5"/>
@@ -7473,7 +7473,7 @@
       <c r="BN21" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO21" s="144">
+      <c r="BO21" s="131">
         <v>1</v>
       </c>
       <c r="BP21" s="5"/>
@@ -7675,7 +7675,7 @@
       <c r="BN22" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO22" s="144">
+      <c r="BO22" s="131">
         <v>3</v>
       </c>
       <c r="BP22" s="5"/>
@@ -7877,7 +7877,7 @@
       <c r="BN23" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO23" s="144">
+      <c r="BO23" s="131">
         <v>0.5</v>
       </c>
       <c r="BP23" s="5"/>
@@ -8079,7 +8079,7 @@
       <c r="BN24" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO24" s="144">
+      <c r="BO24" s="131">
         <v>4</v>
       </c>
       <c r="BP24" s="5"/>
@@ -8281,7 +8281,7 @@
       <c r="BN25" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO25" s="144">
+      <c r="BO25" s="131">
         <v>1</v>
       </c>
       <c r="BP25" s="5"/>
@@ -8481,7 +8481,7 @@
       <c r="BN26" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO26" s="144">
+      <c r="BO26" s="131">
         <v>1</v>
       </c>
       <c r="BP26" s="5"/>
@@ -8681,7 +8681,7 @@
       <c r="BN27" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO27" s="144">
+      <c r="BO27" s="131">
         <v>1</v>
       </c>
       <c r="BP27" s="5"/>
@@ -8881,7 +8881,7 @@
       <c r="BN28" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO28" s="144">
+      <c r="BO28" s="131">
         <v>2</v>
       </c>
       <c r="BP28" s="5"/>
@@ -9083,7 +9083,7 @@
       <c r="BN29" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO29" s="144">
+      <c r="BO29" s="131">
         <v>2</v>
       </c>
       <c r="BP29" s="5"/>
@@ -9283,7 +9283,7 @@
       <c r="BN30" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO30" s="144">
+      <c r="BO30" s="131">
         <v>0.5</v>
       </c>
       <c r="BP30" s="5"/>
@@ -9483,7 +9483,7 @@
       <c r="BN31" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO31" s="144">
+      <c r="BO31" s="131">
         <v>1</v>
       </c>
       <c r="BP31" s="5"/>
@@ -9683,7 +9683,7 @@
       <c r="BN32" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO32" s="144">
+      <c r="BO32" s="131">
         <v>1</v>
       </c>
       <c r="BP32" s="5"/>
@@ -9885,7 +9885,7 @@
       <c r="BN33" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO33" s="144">
+      <c r="BO33" s="131">
         <v>2</v>
       </c>
       <c r="BP33" s="5"/>
@@ -10085,7 +10085,7 @@
       <c r="BN34" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO34" s="144">
+      <c r="BO34" s="131">
         <v>1</v>
       </c>
       <c r="BP34" s="5"/>
@@ -10285,7 +10285,7 @@
       <c r="BN35" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO35" s="144">
+      <c r="BO35" s="131">
         <v>1</v>
       </c>
       <c r="BP35" s="5"/>
@@ -10485,7 +10485,7 @@
       <c r="BN36" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO36" s="144">
+      <c r="BO36" s="131">
         <v>2</v>
       </c>
       <c r="BP36" s="5"/>
@@ -10685,7 +10685,7 @@
       <c r="BN37" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO37" s="144">
+      <c r="BO37" s="131">
         <v>1</v>
       </c>
       <c r="BP37" s="5"/>
@@ -10885,7 +10885,7 @@
       <c r="BN38" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO38" s="144">
+      <c r="BO38" s="131">
         <v>1</v>
       </c>
       <c r="BP38" s="5"/>
@@ -11085,7 +11085,7 @@
       <c r="BN39" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO39" s="144">
+      <c r="BO39" s="131">
         <v>1</v>
       </c>
       <c r="BP39" s="5"/>
@@ -11285,7 +11285,7 @@
       <c r="BN40" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO40" s="144">
+      <c r="BO40" s="131">
         <v>1</v>
       </c>
       <c r="BP40" s="5"/>
@@ -11485,7 +11485,7 @@
       <c r="BN41" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO41" s="144">
+      <c r="BO41" s="131">
         <v>3</v>
       </c>
       <c r="BP41" s="5"/>
@@ -11685,7 +11685,7 @@
       <c r="BN42" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO42" s="144">
+      <c r="BO42" s="131">
         <v>1</v>
       </c>
       <c r="BP42" s="5"/>
@@ -11820,7 +11820,9 @@
       <c r="AQ43" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="AR43" s="7"/>
+      <c r="AR43" s="7">
+        <v>1</v>
+      </c>
       <c r="AS43" s="8" t="s">
         <v>23</v>
       </c>
@@ -11885,7 +11887,7 @@
       <c r="BN43" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO43" s="144">
+      <c r="BO43" s="131">
         <v>1</v>
       </c>
       <c r="BP43" s="5"/>
@@ -12085,7 +12087,7 @@
       <c r="BN44" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO44" s="144">
+      <c r="BO44" s="131">
         <v>0.5</v>
       </c>
       <c r="BP44" s="5"/>
@@ -12285,7 +12287,7 @@
       <c r="BN45" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO45" s="144">
+      <c r="BO45" s="131">
         <v>1</v>
       </c>
       <c r="BP45" s="5"/>
@@ -12485,7 +12487,7 @@
       <c r="BN46" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO46" s="144">
+      <c r="BO46" s="131">
         <v>0.5</v>
       </c>
       <c r="BP46" s="5"/>
@@ -12685,7 +12687,7 @@
       <c r="BN47" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO47" s="144">
+      <c r="BO47" s="131">
         <v>1</v>
       </c>
       <c r="BP47" s="5"/>
@@ -12885,7 +12887,7 @@
       <c r="BN48" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO48" s="144">
+      <c r="BO48" s="131">
         <v>1</v>
       </c>
       <c r="BP48" s="5"/>
@@ -13085,7 +13087,7 @@
       <c r="BN49" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO49" s="144">
+      <c r="BO49" s="131">
         <v>1</v>
       </c>
       <c r="BP49" s="5"/>
@@ -13285,7 +13287,7 @@
       <c r="BN50" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO50" s="144">
+      <c r="BO50" s="131">
         <v>1</v>
       </c>
       <c r="BP50" s="5"/>
@@ -13485,7 +13487,7 @@
       <c r="BN51" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO51" s="144">
+      <c r="BO51" s="131">
         <v>2</v>
       </c>
       <c r="BP51" s="5"/>
@@ -13685,7 +13687,7 @@
       <c r="BN52" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO52" s="144">
+      <c r="BO52" s="131">
         <v>2</v>
       </c>
       <c r="BP52" s="5"/>
@@ -13885,7 +13887,7 @@
       <c r="BN53" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO53" s="144">
+      <c r="BO53" s="131">
         <v>1</v>
       </c>
       <c r="BP53" s="5"/>
@@ -14085,7 +14087,7 @@
       <c r="BN54" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO54" s="144">
+      <c r="BO54" s="131">
         <v>1.5</v>
       </c>
       <c r="BP54" s="5"/>
@@ -14285,7 +14287,7 @@
       <c r="BN55" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO55" s="144">
+      <c r="BO55" s="131">
         <v>1</v>
       </c>
       <c r="BP55" s="5"/>
@@ -14487,7 +14489,7 @@
       <c r="BN56" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO56" s="144">
+      <c r="BO56" s="131">
         <v>2</v>
       </c>
       <c r="BP56" s="5"/>
@@ -14687,7 +14689,7 @@
       <c r="BN57" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO57" s="144">
+      <c r="BO57" s="131">
         <v>1</v>
       </c>
       <c r="BP57" s="5"/>
@@ -14887,7 +14889,7 @@
       <c r="BN58" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO58" s="144">
+      <c r="BO58" s="131">
         <v>1</v>
       </c>
       <c r="BP58" s="5"/>
@@ -15087,7 +15089,7 @@
       <c r="BN59" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO59" s="144">
+      <c r="BO59" s="131">
         <v>1</v>
       </c>
       <c r="BP59" s="5"/>
@@ -15287,7 +15289,7 @@
       <c r="BN60" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO60" s="144">
+      <c r="BO60" s="131">
         <v>1</v>
       </c>
       <c r="BP60" s="5"/>
@@ -15489,7 +15491,7 @@
       <c r="BN61" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO61" s="144">
+      <c r="BO61" s="131">
         <v>2</v>
       </c>
       <c r="BP61" s="5"/>
@@ -15689,7 +15691,7 @@
       <c r="BN62" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO62" s="144">
+      <c r="BO62" s="131">
         <v>1</v>
       </c>
       <c r="BP62" s="5"/>
@@ -15889,7 +15891,7 @@
       <c r="BN63" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO63" s="144">
+      <c r="BO63" s="131">
         <v>1</v>
       </c>
       <c r="BP63" s="5"/>
@@ -16089,7 +16091,7 @@
       <c r="BN64" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO64" s="144">
+      <c r="BO64" s="131">
         <v>1</v>
       </c>
       <c r="BP64" s="5"/>
@@ -16289,7 +16291,7 @@
       <c r="BN65" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO65" s="144">
+      <c r="BO65" s="131">
         <v>1</v>
       </c>
       <c r="BP65" s="5"/>
@@ -16489,7 +16491,7 @@
       <c r="BN66" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO66" s="144">
+      <c r="BO66" s="131">
         <v>1</v>
       </c>
       <c r="BP66" s="5"/>
@@ -16689,7 +16691,7 @@
       <c r="BN67" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO67" s="144">
+      <c r="BO67" s="131">
         <v>1</v>
       </c>
       <c r="BP67" s="5"/>
@@ -16889,7 +16891,7 @@
       <c r="BN68" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO68" s="144">
+      <c r="BO68" s="131">
         <v>1</v>
       </c>
       <c r="BP68" s="5"/>
@@ -17089,7 +17091,7 @@
       <c r="BN69" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO69" s="144">
+      <c r="BO69" s="131">
         <v>1</v>
       </c>
       <c r="BP69" s="5"/>
@@ -17289,7 +17291,7 @@
       <c r="BN70" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO70" s="144">
+      <c r="BO70" s="131">
         <v>1</v>
       </c>
       <c r="BP70" s="5"/>
@@ -17489,7 +17491,7 @@
       <c r="BN71" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO71" s="144">
+      <c r="BO71" s="131">
         <v>1</v>
       </c>
       <c r="BP71" s="5"/>
@@ -17691,7 +17693,7 @@
       <c r="BN72" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO72" s="144">
+      <c r="BO72" s="131">
         <v>1</v>
       </c>
       <c r="BP72" s="5"/>
@@ -17891,7 +17893,7 @@
       <c r="BN73" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO73" s="144">
+      <c r="BO73" s="131">
         <v>2</v>
       </c>
       <c r="BP73" s="5"/>
@@ -18091,7 +18093,7 @@
       <c r="BN74" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO74" s="144">
+      <c r="BO74" s="131">
         <v>0.6</v>
       </c>
       <c r="BP74" s="5"/>
@@ -18291,7 +18293,7 @@
       <c r="BN75" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO75" s="144">
+      <c r="BO75" s="131">
         <v>1</v>
       </c>
       <c r="BP75" s="5"/>
@@ -18493,7 +18495,7 @@
       <c r="BN76" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO76" s="144">
+      <c r="BO76" s="131">
         <v>9</v>
       </c>
       <c r="BP76" s="5"/>
@@ -18693,7 +18695,7 @@
       <c r="BN77" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO77" s="144">
+      <c r="BO77" s="131">
         <v>1</v>
       </c>
       <c r="BP77" s="5"/>
@@ -18893,7 +18895,7 @@
       <c r="BN78" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO78" s="144">
+      <c r="BO78" s="131">
         <v>1</v>
       </c>
       <c r="BP78" s="5"/>
@@ -19093,7 +19095,7 @@
       <c r="BN79" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO79" s="144">
+      <c r="BO79" s="131">
         <v>1.5</v>
       </c>
       <c r="BP79" s="5"/>
@@ -19293,7 +19295,7 @@
       <c r="BN80" s="114" t="s">
         <v>96</v>
       </c>
-      <c r="BO80" s="144">
+      <c r="BO80" s="131">
         <v>1</v>
       </c>
       <c r="BP80" s="120"/>
@@ -19377,6 +19379,11 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="13">
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="AB1:AD1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="BH1:BM1"/>
     <mergeCell ref="AH1:AJ1"/>
@@ -19385,11 +19392,6 @@
     <mergeCell ref="AZ1:BG1"/>
     <mergeCell ref="AU1:AY1"/>
     <mergeCell ref="AR1:AT1"/>
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="AB1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="U4 BL4 BK5 BM6 BL7 U8 BI8 T9 BH9 BK10:BK14 U14 BM15 U17 BH19 BK20 BL21 U22 BK22 BH23 BI24 U24:U25 BM25 BK26:BK27 BL28 BI29 U29:U30 BH30 U33 BJ33 BK34:BK36 U35 T36 U37 BL37 U39 BM41 BM52 BK53:BK55 T56 BM56 U57 U61 BI61 U70 U72 T76 BJ76 BH77:BH78 BK16:BK18 BK63:BK75 BK57:BK60 BK38:BK40 BI79 BK42:BK51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D372A0FD-832E-4222-9FD4-7DF1139AB725}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C29B14-3866-4013-8295-CA95921C0903}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2963,6 +2963,30 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2976,30 +3000,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3355,107 +3355,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:70" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="137" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="138" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="135"/>
+      <c r="R1" s="133" t="s">
         <v>229</v>
       </c>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="138" t="s">
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="135"/>
+      <c r="V1" s="133" t="s">
         <v>230</v>
       </c>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="144" t="s">
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="136"/>
+      <c r="AA1" s="135"/>
+      <c r="AB1" s="138" t="s">
         <v>231</v>
       </c>
       <c r="AC1" s="139"/>
-      <c r="AD1" s="145"/>
+      <c r="AD1" s="140"/>
       <c r="AE1" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="AF1" s="138" t="s">
+      <c r="AF1" s="133" t="s">
         <v>233</v>
       </c>
-      <c r="AG1" s="140"/>
-      <c r="AH1" s="138" t="s">
+      <c r="AG1" s="135"/>
+      <c r="AH1" s="133" t="s">
         <v>234</v>
       </c>
       <c r="AI1" s="139"/>
-      <c r="AJ1" s="140"/>
-      <c r="AK1" s="138" t="s">
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="133" t="s">
         <v>235</v>
       </c>
-      <c r="AL1" s="140"/>
-      <c r="AM1" s="138" t="s">
+      <c r="AL1" s="135"/>
+      <c r="AM1" s="133" t="s">
         <v>236</v>
       </c>
-      <c r="AN1" s="141"/>
-      <c r="AO1" s="140"/>
+      <c r="AN1" s="134"/>
+      <c r="AO1" s="135"/>
       <c r="AP1" s="65" t="s">
         <v>237</v>
       </c>
       <c r="AQ1" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="AR1" s="133" t="s">
+      <c r="AR1" s="141" t="s">
         <v>239</v>
       </c>
-      <c r="AS1" s="134"/>
-      <c r="AT1" s="135"/>
-      <c r="AU1" s="136" t="s">
+      <c r="AS1" s="142"/>
+      <c r="AT1" s="143"/>
+      <c r="AU1" s="144" t="s">
         <v>240</v>
       </c>
-      <c r="AV1" s="134"/>
-      <c r="AW1" s="134"/>
-      <c r="AX1" s="134"/>
-      <c r="AY1" s="135"/>
-      <c r="AZ1" s="138" t="s">
+      <c r="AV1" s="142"/>
+      <c r="AW1" s="142"/>
+      <c r="AX1" s="142"/>
+      <c r="AY1" s="143"/>
+      <c r="AZ1" s="133" t="s">
         <v>406</v>
       </c>
-      <c r="BA1" s="138"/>
-      <c r="BB1" s="138"/>
-      <c r="BC1" s="138"/>
-      <c r="BD1" s="141"/>
-      <c r="BE1" s="141"/>
-      <c r="BF1" s="141"/>
-      <c r="BG1" s="140"/>
-      <c r="BH1" s="136" t="s">
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="133"/>
+      <c r="BC1" s="133"/>
+      <c r="BD1" s="134"/>
+      <c r="BE1" s="134"/>
+      <c r="BF1" s="134"/>
+      <c r="BG1" s="135"/>
+      <c r="BH1" s="144" t="s">
         <v>241</v>
       </c>
-      <c r="BI1" s="134"/>
-      <c r="BJ1" s="134"/>
-      <c r="BK1" s="134"/>
-      <c r="BL1" s="134"/>
-      <c r="BM1" s="137"/>
-      <c r="BN1" s="133" t="s">
+      <c r="BI1" s="142"/>
+      <c r="BJ1" s="142"/>
+      <c r="BK1" s="142"/>
+      <c r="BL1" s="142"/>
+      <c r="BM1" s="145"/>
+      <c r="BN1" s="141" t="s">
         <v>607</v>
       </c>
-      <c r="BO1" s="134"/>
-      <c r="BP1" s="134"/>
-      <c r="BQ1" s="135"/>
+      <c r="BO1" s="142"/>
+      <c r="BP1" s="142"/>
+      <c r="BQ1" s="143"/>
       <c r="BR1" s="11"/>
     </row>
     <row r="2" spans="1:70" ht="61.8" thickBot="1">
@@ -13605,13 +13605,13 @@
         <v>96</v>
       </c>
       <c r="AL52" s="24">
-        <v>18</v>
+        <v>24.5</v>
       </c>
       <c r="AM52" s="64" t="s">
         <v>96</v>
       </c>
       <c r="AN52" s="15">
-        <v>2</v>
+        <v>14.5</v>
       </c>
       <c r="AO52" s="23" t="s">
         <v>95</v>
@@ -19379,11 +19379,6 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="13">
-    <mergeCell ref="R1:U1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="AB1:AD1"/>
     <mergeCell ref="BN1:BQ1"/>
     <mergeCell ref="BH1:BM1"/>
     <mergeCell ref="AH1:AJ1"/>
@@ -19392,6 +19387,11 @@
     <mergeCell ref="AZ1:BG1"/>
     <mergeCell ref="AU1:AY1"/>
     <mergeCell ref="AR1:AT1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:AA1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="AB1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="U4 BL4 BK5 BM6 BL7 U8 BI8 T9 BH9 BK10:BK14 U14 BM15 U17 BH19 BK20 BL21 U22 BK22 BH23 BI24 U24:U25 BM25 BK26:BK27 BL28 BI29 U29:U30 BH30 U33 BJ33 BK34:BK36 U35 T36 U37 BL37 U39 BM41 BM52 BK53:BK55 T56 BM56 U57 U61 BI61 U70 U72 T76 BJ76 BH77:BH78 BK16:BK18 BK63:BK75 BK57:BK60 BK38:BK40 BI79 BK42:BK51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521204A5-BA12-4BEE-9CD4-9F6646CE43C4}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8745B52A-EA2F-4B04-BA33-70AB38F3CAA8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4173" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4175" uniqueCount="690">
   <si>
     <t>Подразделение</t>
   </si>
@@ -2096,6 +2096,9 @@
   </si>
   <si>
     <t>=A1-D1</t>
+  </si>
+  <si>
+    <t>15+3</t>
   </si>
 </sst>
 </file>
@@ -3244,6 +3247,43 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3258,43 +3298,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3649,44 +3652,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="142" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="141"/>
-      <c r="H1" s="141"/>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
       <c r="R1" s="140"/>
       <c r="S1" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
       <c r="V1" s="140"/>
       <c r="W1" s="138" t="s">
         <v>230</v>
       </c>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="142"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="139"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
       <c r="AB1" s="140"/>
-      <c r="AC1" s="144" t="s">
+      <c r="AC1" s="143" t="s">
         <v>231</v>
       </c>
-      <c r="AD1" s="139"/>
+      <c r="AD1" s="144"/>
       <c r="AE1" s="145"/>
       <c r="AF1" s="50" t="s">
         <v>232</v>
@@ -3698,7 +3701,7 @@
       <c r="AI1" s="138" t="s">
         <v>234</v>
       </c>
-      <c r="AJ1" s="139"/>
+      <c r="AJ1" s="144"/>
       <c r="AK1" s="140"/>
       <c r="AL1" s="138" t="s">
         <v>235</v>
@@ -3707,7 +3710,7 @@
       <c r="AN1" s="138" t="s">
         <v>236</v>
       </c>
-      <c r="AO1" s="141"/>
+      <c r="AO1" s="139"/>
       <c r="AP1" s="140"/>
       <c r="AQ1" s="65" t="s">
         <v>237</v>
@@ -3715,42 +3718,42 @@
       <c r="AR1" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="AS1" s="133" t="s">
+      <c r="AS1" s="146" t="s">
         <v>239</v>
       </c>
-      <c r="AT1" s="134"/>
-      <c r="AU1" s="135"/>
-      <c r="AV1" s="136" t="s">
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="148"/>
+      <c r="AV1" s="149" t="s">
         <v>240</v>
       </c>
-      <c r="AW1" s="134"/>
-      <c r="AX1" s="134"/>
-      <c r="AY1" s="134"/>
-      <c r="AZ1" s="135"/>
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
       <c r="BA1" s="138" t="s">
         <v>406</v>
       </c>
       <c r="BB1" s="138"/>
       <c r="BC1" s="138"/>
       <c r="BD1" s="138"/>
-      <c r="BE1" s="141"/>
-      <c r="BF1" s="141"/>
-      <c r="BG1" s="141"/>
+      <c r="BE1" s="139"/>
+      <c r="BF1" s="139"/>
+      <c r="BG1" s="139"/>
       <c r="BH1" s="140"/>
-      <c r="BI1" s="136" t="s">
+      <c r="BI1" s="149" t="s">
         <v>241</v>
       </c>
-      <c r="BJ1" s="134"/>
-      <c r="BK1" s="134"/>
-      <c r="BL1" s="134"/>
-      <c r="BM1" s="134"/>
-      <c r="BN1" s="137"/>
-      <c r="BO1" s="133" t="s">
+      <c r="BJ1" s="147"/>
+      <c r="BK1" s="147"/>
+      <c r="BL1" s="147"/>
+      <c r="BM1" s="147"/>
+      <c r="BN1" s="150"/>
+      <c r="BO1" s="146" t="s">
         <v>607</v>
       </c>
-      <c r="BP1" s="134"/>
-      <c r="BQ1" s="134"/>
-      <c r="BR1" s="135"/>
+      <c r="BP1" s="147"/>
+      <c r="BQ1" s="147"/>
+      <c r="BR1" s="148"/>
       <c r="BS1" s="11"/>
     </row>
     <row r="2" spans="1:71" ht="61.8" thickBot="1">
@@ -3985,7 +3988,7 @@
       <c r="F3" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="G3" s="150">
+      <c r="G3" s="137">
         <v>41104</v>
       </c>
       <c r="H3" s="37" t="s">
@@ -4188,7 +4191,7 @@
       <c r="F4" s="37" t="s">
         <v>454</v>
       </c>
-      <c r="G4" s="150">
+      <c r="G4" s="137">
         <v>41608</v>
       </c>
       <c r="H4" s="37" t="s">
@@ -4391,7 +4394,7 @@
       <c r="F5" s="37" t="s">
         <v>455</v>
       </c>
-      <c r="G5" s="150">
+      <c r="G5" s="137">
         <v>41759</v>
       </c>
       <c r="H5" s="37" t="s">
@@ -4594,7 +4597,7 @@
       <c r="F6" s="37" t="s">
         <v>457</v>
       </c>
-      <c r="G6" s="150">
+      <c r="G6" s="137">
         <v>41971</v>
       </c>
       <c r="H6" s="37" t="s">
@@ -4797,7 +4800,7 @@
       <c r="F7" s="37" t="s">
         <v>459</v>
       </c>
-      <c r="G7" s="150">
+      <c r="G7" s="137">
         <v>42215</v>
       </c>
       <c r="H7" s="37" t="s">
@@ -5000,7 +5003,7 @@
       <c r="F8" s="37" t="s">
         <v>463</v>
       </c>
-      <c r="G8" s="150">
+      <c r="G8" s="137">
         <v>43077</v>
       </c>
       <c r="H8" s="37" t="s">
@@ -5066,8 +5069,8 @@
       <c r="AB8" s="68">
         <v>3</v>
       </c>
-      <c r="AC8" s="7">
-        <v>12</v>
+      <c r="AC8" s="7" t="s">
+        <v>689</v>
       </c>
       <c r="AD8" s="2" t="s">
         <v>99</v>
@@ -5079,10 +5082,10 @@
         <v>7</v>
       </c>
       <c r="AG8" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH8" s="30">
-        <v>48</v>
+        <v>80</v>
+      </c>
+      <c r="AH8" s="29" t="s">
+        <v>23</v>
       </c>
       <c r="AI8" s="27" t="s">
         <v>96</v>
@@ -5097,7 +5100,7 @@
         <v>96</v>
       </c>
       <c r="AM8" s="24">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="AN8" s="64" t="s">
         <v>96</v>
@@ -5205,7 +5208,7 @@
       <c r="F9" s="37" t="s">
         <v>465</v>
       </c>
-      <c r="G9" s="150">
+      <c r="G9" s="137">
         <v>43454</v>
       </c>
       <c r="H9" s="37" t="s">
@@ -5410,7 +5413,7 @@
       <c r="F10" s="37" t="s">
         <v>467</v>
       </c>
-      <c r="G10" s="150">
+      <c r="G10" s="137">
         <v>43280</v>
       </c>
       <c r="H10" s="37" t="s">
@@ -5613,7 +5616,7 @@
       <c r="F11" s="37" t="s">
         <v>469</v>
       </c>
-      <c r="G11" s="150">
+      <c r="G11" s="137">
         <v>43628</v>
       </c>
       <c r="H11" s="37" t="s">
@@ -5818,7 +5821,7 @@
       <c r="F12" s="37" t="s">
         <v>471</v>
       </c>
-      <c r="G12" s="150">
+      <c r="G12" s="137">
         <v>43784</v>
       </c>
       <c r="H12" s="37" t="s">
@@ -6023,7 +6026,7 @@
       <c r="F13" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="G13" s="150">
+      <c r="G13" s="137">
         <v>43720</v>
       </c>
       <c r="H13" s="37" t="s">
@@ -6226,7 +6229,7 @@
       <c r="F14" s="37" t="s">
         <v>475</v>
       </c>
-      <c r="G14" s="150">
+      <c r="G14" s="137">
         <v>43712</v>
       </c>
       <c r="H14" s="37" t="s">
@@ -6431,7 +6434,7 @@
       <c r="F15" s="37" t="s">
         <v>477</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="137">
         <v>43786</v>
       </c>
       <c r="H15" s="37" t="s">
@@ -6634,7 +6637,7 @@
       <c r="F16" s="37" t="s">
         <v>479</v>
       </c>
-      <c r="G16" s="150">
+      <c r="G16" s="137">
         <v>43790</v>
       </c>
       <c r="H16" s="37" t="s">
@@ -6837,7 +6840,7 @@
       <c r="F17" s="37" t="s">
         <v>482</v>
       </c>
-      <c r="G17" s="150">
+      <c r="G17" s="137">
         <v>44147</v>
       </c>
       <c r="H17" s="37" t="s">
@@ -7042,7 +7045,7 @@
       <c r="F18" s="37" t="s">
         <v>482</v>
       </c>
-      <c r="G18" s="150">
+      <c r="G18" s="137">
         <v>43999</v>
       </c>
       <c r="H18" s="37" t="s">
@@ -7245,7 +7248,7 @@
       <c r="F19" s="37" t="s">
         <v>486</v>
       </c>
-      <c r="G19" s="150">
+      <c r="G19" s="137">
         <v>44599</v>
       </c>
       <c r="H19" s="37" t="s">
@@ -7448,7 +7451,7 @@
       <c r="F20" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="G20" s="150">
+      <c r="G20" s="137">
         <v>44111</v>
       </c>
       <c r="H20" s="37" t="s">
@@ -7651,7 +7654,7 @@
       <c r="F21" s="37" t="s">
         <v>490</v>
       </c>
-      <c r="G21" s="150">
+      <c r="G21" s="137">
         <v>43990</v>
       </c>
       <c r="H21" s="37" t="s">
@@ -7854,7 +7857,7 @@
       <c r="F22" s="37" t="s">
         <v>491</v>
       </c>
-      <c r="G22" s="150">
+      <c r="G22" s="137">
         <v>44156</v>
       </c>
       <c r="H22" s="37" t="s">
@@ -8059,7 +8062,7 @@
       <c r="F23" s="37" t="s">
         <v>494</v>
       </c>
-      <c r="G23" s="150">
+      <c r="G23" s="137">
         <v>44278</v>
       </c>
       <c r="H23" s="37" t="s">
@@ -8264,7 +8267,7 @@
       <c r="F24" s="37" t="s">
         <v>496</v>
       </c>
-      <c r="G24" s="150">
+      <c r="G24" s="137">
         <v>44369</v>
       </c>
       <c r="H24" s="37" t="s">
@@ -8469,7 +8472,7 @@
       <c r="F25" s="37" t="s">
         <v>498</v>
       </c>
-      <c r="G25" s="150">
+      <c r="G25" s="137">
         <v>44266</v>
       </c>
       <c r="H25" s="37" t="s">
@@ -8674,7 +8677,7 @@
       <c r="F26" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G26" s="150">
+      <c r="G26" s="137">
         <v>44201</v>
       </c>
       <c r="H26" s="37" t="s">
@@ -8877,7 +8880,7 @@
       <c r="F27" s="37" t="s">
         <v>502</v>
       </c>
-      <c r="G27" s="150">
+      <c r="G27" s="137">
         <v>44216</v>
       </c>
       <c r="H27" s="37" t="s">
@@ -9080,7 +9083,7 @@
       <c r="F28" s="37" t="s">
         <v>504</v>
       </c>
-      <c r="G28" s="150">
+      <c r="G28" s="137">
         <v>44193</v>
       </c>
       <c r="H28" s="37" t="s">
@@ -9283,7 +9286,7 @@
       <c r="F29" s="37" t="s">
         <v>506</v>
       </c>
-      <c r="G29" s="150">
+      <c r="G29" s="137">
         <v>44273</v>
       </c>
       <c r="H29" s="37" t="s">
@@ -9488,7 +9491,7 @@
       <c r="F30" s="37" t="s">
         <v>508</v>
       </c>
-      <c r="G30" s="150">
+      <c r="G30" s="137">
         <v>44300</v>
       </c>
       <c r="H30" s="37" t="s">
@@ -9691,7 +9694,7 @@
       <c r="F31" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G31" s="150">
+      <c r="G31" s="137">
         <v>44294</v>
       </c>
       <c r="H31" s="37" t="s">
@@ -9894,7 +9897,7 @@
       <c r="F32" s="37" t="s">
         <v>500</v>
       </c>
-      <c r="G32" s="150">
+      <c r="G32" s="137">
         <v>44278</v>
       </c>
       <c r="H32" s="37" t="s">
@@ -10097,7 +10100,7 @@
       <c r="F33" s="37" t="s">
         <v>512</v>
       </c>
-      <c r="G33" s="150">
+      <c r="G33" s="137">
         <v>44350</v>
       </c>
       <c r="H33" s="37" t="s">
@@ -10302,7 +10305,7 @@
       <c r="F34" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G34" s="150">
+      <c r="G34" s="137">
         <v>44377</v>
       </c>
       <c r="H34" s="37" t="s">
@@ -10505,7 +10508,7 @@
       <c r="F35" s="37" t="s">
         <v>515</v>
       </c>
-      <c r="G35" s="150">
+      <c r="G35" s="137">
         <v>44392</v>
       </c>
       <c r="H35" s="37" t="s">
@@ -10708,7 +10711,7 @@
       <c r="F36" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G36" s="150">
+      <c r="G36" s="137">
         <v>44355</v>
       </c>
       <c r="H36" s="37" t="s">
@@ -10911,7 +10914,7 @@
       <c r="F37" s="37" t="s">
         <v>518</v>
       </c>
-      <c r="G37" s="150">
+      <c r="G37" s="137">
         <v>44431</v>
       </c>
       <c r="H37" s="37" t="s">
@@ -11114,7 +11117,7 @@
       <c r="F38" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G38" s="150">
+      <c r="G38" s="137">
         <v>44380</v>
       </c>
       <c r="H38" s="37" t="s">
@@ -11317,7 +11320,7 @@
       <c r="F39" s="37" t="s">
         <v>521</v>
       </c>
-      <c r="G39" s="150">
+      <c r="G39" s="137">
         <v>44403</v>
       </c>
       <c r="H39" s="37" t="s">
@@ -11520,7 +11523,7 @@
       <c r="F40" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G40" s="150">
+      <c r="G40" s="137">
         <v>44366</v>
       </c>
       <c r="H40" s="37" t="s">
@@ -11723,7 +11726,7 @@
       <c r="F41" s="37" t="s">
         <v>525</v>
       </c>
-      <c r="G41" s="150">
+      <c r="G41" s="137">
         <v>44440</v>
       </c>
       <c r="H41" s="37" t="s">
@@ -11926,7 +11929,7 @@
       <c r="F42" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G42" s="150">
+      <c r="G42" s="137">
         <v>44403</v>
       </c>
       <c r="H42" s="37" t="s">
@@ -12129,7 +12132,7 @@
       <c r="F43" s="37" t="s">
         <v>528</v>
       </c>
-      <c r="G43" s="150">
+      <c r="G43" s="137">
         <v>44399</v>
       </c>
       <c r="H43" s="37" t="s">
@@ -12334,7 +12337,7 @@
       <c r="F44" s="37" t="s">
         <v>530</v>
       </c>
-      <c r="G44" s="150">
+      <c r="G44" s="137">
         <v>44464</v>
       </c>
       <c r="H44" s="37" t="s">
@@ -12537,7 +12540,7 @@
       <c r="F45" s="37" t="s">
         <v>532</v>
       </c>
-      <c r="G45" s="150">
+      <c r="G45" s="137">
         <v>44489</v>
       </c>
       <c r="H45" s="37" t="s">
@@ -12740,7 +12743,7 @@
       <c r="F46" s="37" t="s">
         <v>534</v>
       </c>
-      <c r="G46" s="150">
+      <c r="G46" s="137">
         <v>44498</v>
       </c>
       <c r="H46" s="37" t="s">
@@ -12943,7 +12946,7 @@
       <c r="F47" s="37" t="s">
         <v>536</v>
       </c>
-      <c r="G47" s="150">
+      <c r="G47" s="137">
         <v>44638</v>
       </c>
       <c r="H47" s="37" t="s">
@@ -13146,7 +13149,7 @@
       <c r="F48" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G48" s="150">
+      <c r="G48" s="137">
         <v>44559</v>
       </c>
       <c r="H48" s="37" t="s">
@@ -13349,7 +13352,7 @@
       <c r="F49" s="37" t="s">
         <v>539</v>
       </c>
-      <c r="G49" s="150">
+      <c r="G49" s="137">
         <v>44684</v>
       </c>
       <c r="H49" s="37" t="s">
@@ -13552,7 +13555,7 @@
       <c r="F50" s="37" t="s">
         <v>532</v>
       </c>
-      <c r="G50" s="150">
+      <c r="G50" s="137">
         <v>44706</v>
       </c>
       <c r="H50" s="37" t="s">
@@ -13755,7 +13758,7 @@
       <c r="F51" s="37" t="s">
         <v>542</v>
       </c>
-      <c r="G51" s="150">
+      <c r="G51" s="137">
         <v>44715</v>
       </c>
       <c r="H51" s="37" t="s">
@@ -13958,7 +13961,7 @@
       <c r="F52" s="37" t="s">
         <v>544</v>
       </c>
-      <c r="G52" s="150">
+      <c r="G52" s="137">
         <v>44714</v>
       </c>
       <c r="H52" s="37" t="s">
@@ -14161,7 +14164,7 @@
       <c r="F53" s="37" t="s">
         <v>521</v>
       </c>
-      <c r="G53" s="150">
+      <c r="G53" s="137">
         <v>44727</v>
       </c>
       <c r="H53" s="37" t="s">
@@ -14364,7 +14367,7 @@
       <c r="F54" s="37" t="s">
         <v>547</v>
       </c>
-      <c r="G54" s="150">
+      <c r="G54" s="137">
         <v>44693</v>
       </c>
       <c r="H54" s="37" t="s">
@@ -14567,7 +14570,7 @@
       <c r="F55" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G55" s="150">
+      <c r="G55" s="137">
         <v>44764</v>
       </c>
       <c r="H55" s="37" t="s">
@@ -14770,7 +14773,7 @@
       <c r="F56" s="37" t="s">
         <v>550</v>
       </c>
-      <c r="G56" s="150">
+      <c r="G56" s="137">
         <v>44786</v>
       </c>
       <c r="H56" s="37" t="s">
@@ -14975,7 +14978,7 @@
       <c r="F57" s="37" t="s">
         <v>552</v>
       </c>
-      <c r="G57" s="150">
+      <c r="G57" s="137">
         <v>44854</v>
       </c>
       <c r="H57" s="37" t="s">
@@ -15178,7 +15181,7 @@
       <c r="F58" s="37" t="s">
         <v>554</v>
       </c>
-      <c r="G58" s="150">
+      <c r="G58" s="137">
         <v>44810</v>
       </c>
       <c r="H58" s="37" t="s">
@@ -15381,7 +15384,7 @@
       <c r="F59" s="37" t="s">
         <v>556</v>
       </c>
-      <c r="G59" s="150">
+      <c r="G59" s="137">
         <v>44834</v>
       </c>
       <c r="H59" s="37" t="s">
@@ -15584,7 +15587,7 @@
       <c r="F60" s="37" t="s">
         <v>558</v>
       </c>
-      <c r="G60" s="150">
+      <c r="G60" s="137">
         <v>44820</v>
       </c>
       <c r="H60" s="37" t="s">
@@ -15787,7 +15790,7 @@
       <c r="F61" s="37" t="s">
         <v>560</v>
       </c>
-      <c r="G61" s="150">
+      <c r="G61" s="137">
         <v>44835</v>
       </c>
       <c r="H61" s="37" t="s">
@@ -15992,7 +15995,7 @@
       <c r="F62" s="37" t="s">
         <v>562</v>
       </c>
-      <c r="G62" s="150">
+      <c r="G62" s="137">
         <v>44869</v>
       </c>
       <c r="H62" s="37" t="s">
@@ -16195,7 +16198,7 @@
       <c r="F63" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G63" s="150">
+      <c r="G63" s="137">
         <v>44849</v>
       </c>
       <c r="H63" s="37" t="s">
@@ -16398,7 +16401,7 @@
       <c r="F64" s="37" t="s">
         <v>565</v>
       </c>
-      <c r="G64" s="150">
+      <c r="G64" s="137">
         <v>44861</v>
       </c>
       <c r="H64" s="37" t="s">
@@ -16601,7 +16604,7 @@
       <c r="F65" s="37" t="s">
         <v>567</v>
       </c>
-      <c r="G65" s="150">
+      <c r="G65" s="137">
         <v>44928</v>
       </c>
       <c r="H65" s="37" t="s">
@@ -16804,7 +16807,7 @@
       <c r="F66" s="37" t="s">
         <v>569</v>
       </c>
-      <c r="G66" s="150">
+      <c r="G66" s="137">
         <v>44905</v>
       </c>
       <c r="H66" s="37" t="s">
@@ -17007,7 +17010,7 @@
       <c r="F67" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G67" s="150">
+      <c r="G67" s="137">
         <v>44965</v>
       </c>
       <c r="H67" s="37" t="s">
@@ -17210,7 +17213,7 @@
       <c r="F68" s="37" t="s">
         <v>572</v>
       </c>
-      <c r="G68" s="150">
+      <c r="G68" s="137">
         <v>44912</v>
       </c>
       <c r="H68" s="37" t="s">
@@ -17413,7 +17416,7 @@
       <c r="F69" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G69" s="150">
+      <c r="G69" s="137">
         <v>45086</v>
       </c>
       <c r="H69" s="37" t="s">
@@ -17616,7 +17619,7 @@
       <c r="F70" s="37" t="s">
         <v>575</v>
       </c>
-      <c r="G70" s="150">
+      <c r="G70" s="137">
         <v>45057</v>
       </c>
       <c r="H70" s="37" t="s">
@@ -17819,7 +17822,7 @@
       <c r="F71" s="37" t="s">
         <v>575</v>
       </c>
-      <c r="G71" s="150">
+      <c r="G71" s="137">
         <v>45085</v>
       </c>
       <c r="H71" s="37" t="s">
@@ -18022,7 +18025,7 @@
       <c r="F72" s="37" t="s">
         <v>480</v>
       </c>
-      <c r="G72" s="150">
+      <c r="G72" s="137">
         <v>45078</v>
       </c>
       <c r="H72" s="37" t="s">
@@ -18227,7 +18230,7 @@
       <c r="F73" s="37" t="s">
         <v>579</v>
       </c>
-      <c r="G73" s="150">
+      <c r="G73" s="137">
         <v>45150</v>
       </c>
       <c r="H73" s="37" t="s">
@@ -18430,7 +18433,7 @@
       <c r="F74" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G74" s="150">
+      <c r="G74" s="137">
         <v>45262</v>
       </c>
       <c r="H74" s="37" t="s">
@@ -18633,7 +18636,7 @@
       <c r="F75" s="37" t="s">
         <v>523</v>
       </c>
-      <c r="G75" s="150">
+      <c r="G75" s="137">
         <v>45278</v>
       </c>
       <c r="H75" s="37" t="s">
@@ -18836,7 +18839,7 @@
       <c r="F76" s="37" t="s">
         <v>586</v>
       </c>
-      <c r="G76" s="150">
+      <c r="G76" s="137">
         <v>45413</v>
       </c>
       <c r="H76" s="37" t="s">
@@ -19041,7 +19044,7 @@
       <c r="F77" s="37" t="s">
         <v>582</v>
       </c>
-      <c r="G77" s="150">
+      <c r="G77" s="137">
         <v>45765</v>
       </c>
       <c r="H77" s="37" t="s">
@@ -19244,7 +19247,7 @@
       <c r="F78" s="37" t="s">
         <v>583</v>
       </c>
-      <c r="G78" s="150">
+      <c r="G78" s="137">
         <v>45892</v>
       </c>
       <c r="H78" s="37" t="s">
@@ -19447,7 +19450,7 @@
       <c r="F79" s="88" t="s">
         <v>584</v>
       </c>
-      <c r="G79" s="150">
+      <c r="G79" s="137">
         <v>46003</v>
       </c>
       <c r="H79" s="88" t="s">
@@ -19650,7 +19653,7 @@
       <c r="F80" s="37" t="s">
         <v>575</v>
       </c>
-      <c r="G80" s="150">
+      <c r="G80" s="137">
         <v>46284</v>
       </c>
       <c r="H80" s="37" t="s">
@@ -19912,11 +19915,6 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="13">
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="BO1:BR1"/>
     <mergeCell ref="BI1:BN1"/>
     <mergeCell ref="AI1:AK1"/>
@@ -19925,6 +19923,11 @@
     <mergeCell ref="BA1:BH1"/>
     <mergeCell ref="AV1:AZ1"/>
     <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="AC1:AE1"/>
   </mergeCells>
   <conditionalFormatting sqref="V4 BM4 BL5 BN6 BM7 V8 BJ8 U9 BI9 BL10:BL14 V14 BN15 V17 BI19 BL20 BM21 V22 BL22 BI23 BJ24 V24:V25 BN25 BL26:BL27 BM28 BJ29 V29:V30 BI30 V33 BK33 BL34:BL36 V35 U36 V37 BM37 V39 BN41 BN52 BL53:BL55 U56 BN56 V57 V61 BJ61 V70 V72 U76 BK76 BI77:BI78 BL16:BL18 BL63:BL75 BL57:BL60 BL38:BL40 BJ79 BL42:BL51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">
@@ -19962,1094 +19965,1094 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="146">
+      <c r="A1" s="133">
         <v>10027</v>
       </c>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="133" t="s">
         <v>611</v>
       </c>
-      <c r="C1" s="147">
+      <c r="C1" s="134">
         <v>41104</v>
       </c>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="133" t="s">
         <v>171</v>
       </c>
-      <c r="F1" s="149" t="s">
+      <c r="F1" s="136" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="146">
+      <c r="A2" s="133">
         <v>10462</v>
       </c>
-      <c r="B2" s="146" t="s">
+      <c r="B2" s="133" t="s">
         <v>612</v>
       </c>
-      <c r="C2" s="147">
+      <c r="C2" s="134">
         <v>41608</v>
       </c>
-      <c r="D2" s="146" t="s">
+      <c r="D2" s="133" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="146">
+      <c r="A3" s="133">
         <v>10541</v>
       </c>
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="133" t="s">
         <v>613</v>
       </c>
-      <c r="C3" s="147">
+      <c r="C3" s="134">
         <v>41759</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="133" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="146">
+      <c r="A4" s="133">
         <v>10625</v>
       </c>
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="133" t="s">
         <v>614</v>
       </c>
-      <c r="C4" s="147">
+      <c r="C4" s="134">
         <v>41971</v>
       </c>
-      <c r="D4" s="146" t="s">
+      <c r="D4" s="133" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="146">
+      <c r="A5" s="133">
         <v>10696</v>
       </c>
-      <c r="B5" s="146" t="s">
+      <c r="B5" s="133" t="s">
         <v>615</v>
       </c>
-      <c r="C5" s="147">
+      <c r="C5" s="134">
         <v>42215</v>
       </c>
-      <c r="D5" s="146" t="s">
+      <c r="D5" s="133" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="146">
+      <c r="A6" s="133">
         <v>10919</v>
       </c>
-      <c r="B6" s="146" t="s">
+      <c r="B6" s="133" t="s">
         <v>616</v>
       </c>
-      <c r="C6" s="147">
+      <c r="C6" s="134">
         <v>43077</v>
       </c>
-      <c r="D6" s="146" t="s">
+      <c r="D6" s="133" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="146">
+      <c r="A7" s="133">
         <v>10949</v>
       </c>
-      <c r="B7" s="146" t="s">
+      <c r="B7" s="133" t="s">
         <v>617</v>
       </c>
-      <c r="C7" s="147">
+      <c r="C7" s="134">
         <v>43454</v>
       </c>
-      <c r="D7" s="146" t="s">
+      <c r="D7" s="133" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="146">
+      <c r="A8" s="133">
         <v>10951</v>
       </c>
-      <c r="B8" s="146" t="s">
+      <c r="B8" s="133" t="s">
         <v>618</v>
       </c>
-      <c r="C8" s="147">
+      <c r="C8" s="134">
         <v>43280</v>
       </c>
-      <c r="D8" s="146" t="s">
+      <c r="D8" s="133" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="146">
+      <c r="A9" s="133">
         <v>11015</v>
       </c>
-      <c r="B9" s="146" t="s">
+      <c r="B9" s="133" t="s">
         <v>619</v>
       </c>
-      <c r="C9" s="147">
+      <c r="C9" s="134">
         <v>43628</v>
       </c>
-      <c r="D9" s="146" t="s">
+      <c r="D9" s="133" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="146">
+      <c r="A10" s="133">
         <v>11063</v>
       </c>
-      <c r="B10" s="146" t="s">
+      <c r="B10" s="133" t="s">
         <v>620</v>
       </c>
-      <c r="C10" s="147">
+      <c r="C10" s="134">
         <v>43784</v>
       </c>
-      <c r="D10" s="146" t="s">
+      <c r="D10" s="133" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="146">
+      <c r="A11" s="133">
         <v>11103</v>
       </c>
-      <c r="B11" s="146" t="s">
+      <c r="B11" s="133" t="s">
         <v>621</v>
       </c>
-      <c r="C11" s="147">
+      <c r="C11" s="134">
         <v>43720</v>
       </c>
-      <c r="D11" s="146" t="s">
+      <c r="D11" s="133" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="146">
+      <c r="A12" s="133">
         <v>11117</v>
       </c>
-      <c r="B12" s="146" t="s">
+      <c r="B12" s="133" t="s">
         <v>622</v>
       </c>
-      <c r="C12" s="147">
+      <c r="C12" s="134">
         <v>43712</v>
       </c>
-      <c r="D12" s="146" t="s">
+      <c r="D12" s="133" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="146">
+      <c r="A13" s="133">
         <v>11143</v>
       </c>
-      <c r="B13" s="146" t="s">
+      <c r="B13" s="133" t="s">
         <v>623</v>
       </c>
-      <c r="C13" s="147">
+      <c r="C13" s="134">
         <v>43786</v>
       </c>
-      <c r="D13" s="146" t="s">
+      <c r="D13" s="133" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="146">
+      <c r="A14" s="133">
         <v>11187</v>
       </c>
-      <c r="B14" s="146" t="s">
+      <c r="B14" s="133" t="s">
         <v>624</v>
       </c>
-      <c r="C14" s="147">
+      <c r="C14" s="134">
         <v>43790</v>
       </c>
-      <c r="D14" s="146" t="s">
+      <c r="D14" s="133" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="146">
+      <c r="A15" s="133">
         <v>11341</v>
       </c>
-      <c r="B15" s="146" t="s">
+      <c r="B15" s="133" t="s">
         <v>625</v>
       </c>
-      <c r="C15" s="147">
+      <c r="C15" s="134">
         <v>44147</v>
       </c>
-      <c r="D15" s="146" t="s">
+      <c r="D15" s="133" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="146">
+      <c r="A16" s="133">
         <v>11352</v>
       </c>
-      <c r="B16" s="146" t="s">
+      <c r="B16" s="133" t="s">
         <v>626</v>
       </c>
-      <c r="C16" s="147">
+      <c r="C16" s="134">
         <v>43999</v>
       </c>
-      <c r="D16" s="146" t="s">
+      <c r="D16" s="133" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="146">
+      <c r="A17" s="133">
         <v>11372</v>
       </c>
-      <c r="B17" s="146" t="s">
+      <c r="B17" s="133" t="s">
         <v>627</v>
       </c>
-      <c r="C17" s="147">
+      <c r="C17" s="134">
         <v>44599</v>
       </c>
-      <c r="D17" s="146" t="s">
+      <c r="D17" s="133" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="146">
+      <c r="A18" s="133">
         <v>11373</v>
       </c>
-      <c r="B18" s="146" t="s">
+      <c r="B18" s="133" t="s">
         <v>628</v>
       </c>
-      <c r="C18" s="147">
+      <c r="C18" s="134">
         <v>44111</v>
       </c>
-      <c r="D18" s="146" t="s">
+      <c r="D18" s="133" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="146">
+      <c r="A19" s="133">
         <v>11374</v>
       </c>
-      <c r="B19" s="146" t="s">
+      <c r="B19" s="133" t="s">
         <v>629</v>
       </c>
-      <c r="C19" s="147">
+      <c r="C19" s="134">
         <v>43990</v>
       </c>
-      <c r="D19" s="146" t="s">
+      <c r="D19" s="133" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="146">
+      <c r="A20" s="133">
         <v>11385</v>
       </c>
-      <c r="B20" s="146" t="s">
+      <c r="B20" s="133" t="s">
         <v>630</v>
       </c>
-      <c r="C20" s="147">
+      <c r="C20" s="134">
         <v>44156</v>
       </c>
-      <c r="D20" s="146" t="s">
+      <c r="D20" s="133" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="146">
+      <c r="A21" s="133">
         <v>11404</v>
       </c>
-      <c r="B21" s="146" t="s">
+      <c r="B21" s="133" t="s">
         <v>631</v>
       </c>
-      <c r="C21" s="147">
+      <c r="C21" s="134">
         <v>44278</v>
       </c>
-      <c r="D21" s="146" t="s">
+      <c r="D21" s="133" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="146">
+      <c r="A22" s="133">
         <v>11418</v>
       </c>
-      <c r="B22" s="146" t="s">
+      <c r="B22" s="133" t="s">
         <v>632</v>
       </c>
-      <c r="C22" s="147">
+      <c r="C22" s="134">
         <v>44369</v>
       </c>
-      <c r="D22" s="146" t="s">
+      <c r="D22" s="133" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="146">
+      <c r="A23" s="133">
         <v>11422</v>
       </c>
-      <c r="B23" s="146" t="s">
+      <c r="B23" s="133" t="s">
         <v>633</v>
       </c>
-      <c r="C23" s="147">
+      <c r="C23" s="134">
         <v>44266</v>
       </c>
-      <c r="D23" s="146" t="s">
+      <c r="D23" s="133" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="146">
+      <c r="A24" s="133">
         <v>11424</v>
       </c>
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="133" t="s">
         <v>634</v>
       </c>
-      <c r="C24" s="147">
+      <c r="C24" s="134">
         <v>44201</v>
       </c>
-      <c r="D24" s="146" t="s">
+      <c r="D24" s="133" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="146">
+      <c r="A25" s="133">
         <v>11433</v>
       </c>
-      <c r="B25" s="146" t="s">
+      <c r="B25" s="133" t="s">
         <v>635</v>
       </c>
-      <c r="C25" s="147">
+      <c r="C25" s="134">
         <v>44216</v>
       </c>
-      <c r="D25" s="146" t="s">
+      <c r="D25" s="133" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="146">
+      <c r="A26" s="133">
         <v>11435</v>
       </c>
-      <c r="B26" s="146" t="s">
+      <c r="B26" s="133" t="s">
         <v>636</v>
       </c>
-      <c r="C26" s="147">
+      <c r="C26" s="134">
         <v>44193</v>
       </c>
-      <c r="D26" s="146" t="s">
+      <c r="D26" s="133" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="146">
+      <c r="A27" s="133">
         <v>11437</v>
       </c>
-      <c r="B27" s="146" t="s">
+      <c r="B27" s="133" t="s">
         <v>637</v>
       </c>
-      <c r="C27" s="147">
+      <c r="C27" s="134">
         <v>44273</v>
       </c>
-      <c r="D27" s="146" t="s">
+      <c r="D27" s="133" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="146">
+      <c r="A28" s="133">
         <v>11439</v>
       </c>
-      <c r="B28" s="146" t="s">
+      <c r="B28" s="133" t="s">
         <v>638</v>
       </c>
-      <c r="C28" s="147">
+      <c r="C28" s="134">
         <v>44300</v>
       </c>
-      <c r="D28" s="146" t="s">
+      <c r="D28" s="133" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="146">
+      <c r="A29" s="133">
         <v>11448</v>
       </c>
-      <c r="B29" s="146" t="s">
+      <c r="B29" s="133" t="s">
         <v>639</v>
       </c>
-      <c r="C29" s="147">
+      <c r="C29" s="134">
         <v>44294</v>
       </c>
-      <c r="D29" s="146" t="s">
+      <c r="D29" s="133" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="146">
+      <c r="A30" s="133">
         <v>11455</v>
       </c>
-      <c r="B30" s="146" t="s">
+      <c r="B30" s="133" t="s">
         <v>640</v>
       </c>
-      <c r="C30" s="147">
+      <c r="C30" s="134">
         <v>44278</v>
       </c>
-      <c r="D30" s="146" t="s">
+      <c r="D30" s="133" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="146">
+      <c r="A31" s="133">
         <v>11472</v>
       </c>
-      <c r="B31" s="146" t="s">
+      <c r="B31" s="133" t="s">
         <v>641</v>
       </c>
-      <c r="C31" s="147">
+      <c r="C31" s="134">
         <v>44350</v>
       </c>
-      <c r="D31" s="146" t="s">
+      <c r="D31" s="133" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="146">
+      <c r="A32" s="133">
         <v>11490</v>
       </c>
-      <c r="B32" s="146" t="s">
+      <c r="B32" s="133" t="s">
         <v>642</v>
       </c>
-      <c r="C32" s="147">
+      <c r="C32" s="134">
         <v>44377</v>
       </c>
-      <c r="D32" s="146" t="s">
+      <c r="D32" s="133" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="146">
+      <c r="A33" s="133">
         <v>11495</v>
       </c>
-      <c r="B33" s="146" t="s">
+      <c r="B33" s="133" t="s">
         <v>643</v>
       </c>
-      <c r="C33" s="147">
+      <c r="C33" s="134">
         <v>44392</v>
       </c>
-      <c r="D33" s="146" t="s">
+      <c r="D33" s="133" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="146">
+      <c r="A34" s="133">
         <v>11501</v>
       </c>
-      <c r="B34" s="146" t="s">
+      <c r="B34" s="133" t="s">
         <v>644</v>
       </c>
-      <c r="C34" s="147">
+      <c r="C34" s="134">
         <v>44355</v>
       </c>
-      <c r="D34" s="146" t="s">
+      <c r="D34" s="133" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="146">
+      <c r="A35" s="133">
         <v>11509</v>
       </c>
-      <c r="B35" s="146" t="s">
+      <c r="B35" s="133" t="s">
         <v>645</v>
       </c>
-      <c r="C35" s="147">
+      <c r="C35" s="134">
         <v>44431</v>
       </c>
-      <c r="D35" s="146" t="s">
+      <c r="D35" s="133" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="146">
+      <c r="A36" s="133">
         <v>11518</v>
       </c>
-      <c r="B36" s="146" t="s">
+      <c r="B36" s="133" t="s">
         <v>646</v>
       </c>
-      <c r="C36" s="147">
+      <c r="C36" s="134">
         <v>44380</v>
       </c>
-      <c r="D36" s="146" t="s">
+      <c r="D36" s="133" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="146">
+      <c r="A37" s="133">
         <v>11521</v>
       </c>
-      <c r="B37" s="146" t="s">
+      <c r="B37" s="133" t="s">
         <v>647</v>
       </c>
-      <c r="C37" s="147">
+      <c r="C37" s="134">
         <v>44403</v>
       </c>
-      <c r="D37" s="146" t="s">
+      <c r="D37" s="133" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="146">
+      <c r="A38" s="133">
         <v>11525</v>
       </c>
-      <c r="B38" s="146" t="s">
+      <c r="B38" s="133" t="s">
         <v>648</v>
       </c>
-      <c r="C38" s="147">
+      <c r="C38" s="134">
         <v>44366</v>
       </c>
-      <c r="D38" s="146" t="s">
+      <c r="D38" s="133" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="146">
+      <c r="A39" s="133">
         <v>11529</v>
       </c>
-      <c r="B39" s="146" t="s">
+      <c r="B39" s="133" t="s">
         <v>649</v>
       </c>
-      <c r="C39" s="147">
+      <c r="C39" s="134">
         <v>44440</v>
       </c>
-      <c r="D39" s="146" t="s">
+      <c r="D39" s="133" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="146">
+      <c r="A40" s="133">
         <v>11534</v>
       </c>
-      <c r="B40" s="146" t="s">
+      <c r="B40" s="133" t="s">
         <v>650</v>
       </c>
-      <c r="C40" s="147">
+      <c r="C40" s="134">
         <v>44403</v>
       </c>
-      <c r="D40" s="146" t="s">
+      <c r="D40" s="133" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="146">
+      <c r="A41" s="133">
         <v>11557</v>
       </c>
-      <c r="B41" s="146" t="s">
+      <c r="B41" s="133" t="s">
         <v>651</v>
       </c>
-      <c r="C41" s="147">
+      <c r="C41" s="134">
         <v>44399</v>
       </c>
-      <c r="D41" s="146" t="s">
+      <c r="D41" s="133" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="146">
+      <c r="A42" s="133">
         <v>11567</v>
       </c>
-      <c r="B42" s="146" t="s">
+      <c r="B42" s="133" t="s">
         <v>652</v>
       </c>
-      <c r="C42" s="147">
+      <c r="C42" s="134">
         <v>44464</v>
       </c>
-      <c r="D42" s="146" t="s">
+      <c r="D42" s="133" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="146">
+      <c r="A43" s="133">
         <v>11605</v>
       </c>
-      <c r="B43" s="146" t="s">
+      <c r="B43" s="133" t="s">
         <v>653</v>
       </c>
-      <c r="C43" s="147">
+      <c r="C43" s="134">
         <v>44489</v>
       </c>
-      <c r="D43" s="146" t="s">
+      <c r="D43" s="133" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="146">
+      <c r="A44" s="133">
         <v>11621</v>
       </c>
-      <c r="B44" s="146" t="s">
+      <c r="B44" s="133" t="s">
         <v>654</v>
       </c>
-      <c r="C44" s="147">
+      <c r="C44" s="134">
         <v>44498</v>
       </c>
-      <c r="D44" s="146" t="s">
+      <c r="D44" s="133" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="146">
+      <c r="A45" s="133">
         <v>11639</v>
       </c>
-      <c r="B45" s="146" t="s">
+      <c r="B45" s="133" t="s">
         <v>655</v>
       </c>
-      <c r="C45" s="147">
+      <c r="C45" s="134">
         <v>44638</v>
       </c>
-      <c r="D45" s="146" t="s">
+      <c r="D45" s="133" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="146">
+      <c r="A46" s="133">
         <v>11647</v>
       </c>
-      <c r="B46" s="146" t="s">
+      <c r="B46" s="133" t="s">
         <v>656</v>
       </c>
-      <c r="C46" s="147">
+      <c r="C46" s="134">
         <v>44559</v>
       </c>
-      <c r="D46" s="146" t="s">
+      <c r="D46" s="133" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="146">
+      <c r="A47" s="133">
         <v>11703</v>
       </c>
-      <c r="B47" s="146" t="s">
+      <c r="B47" s="133" t="s">
         <v>657</v>
       </c>
-      <c r="C47" s="147">
+      <c r="C47" s="134">
         <v>44684</v>
       </c>
-      <c r="D47" s="146" t="s">
+      <c r="D47" s="133" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="146">
+      <c r="A48" s="133">
         <v>11729</v>
       </c>
-      <c r="B48" s="146" t="s">
+      <c r="B48" s="133" t="s">
         <v>658</v>
       </c>
-      <c r="C48" s="147">
+      <c r="C48" s="134">
         <v>44706</v>
       </c>
-      <c r="D48" s="146" t="s">
+      <c r="D48" s="133" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="146">
+      <c r="A49" s="133">
         <v>11731</v>
       </c>
-      <c r="B49" s="146" t="s">
+      <c r="B49" s="133" t="s">
         <v>659</v>
       </c>
-      <c r="C49" s="147">
+      <c r="C49" s="134">
         <v>44715</v>
       </c>
-      <c r="D49" s="146" t="s">
+      <c r="D49" s="133" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="146">
+      <c r="A50" s="133">
         <v>11735</v>
       </c>
-      <c r="B50" s="146" t="s">
+      <c r="B50" s="133" t="s">
         <v>660</v>
       </c>
-      <c r="C50" s="147">
+      <c r="C50" s="134">
         <v>44714</v>
       </c>
-      <c r="D50" s="146" t="s">
+      <c r="D50" s="133" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="146">
+      <c r="A51" s="133">
         <v>11759</v>
       </c>
-      <c r="B51" s="146" t="s">
+      <c r="B51" s="133" t="s">
         <v>661</v>
       </c>
-      <c r="C51" s="147">
+      <c r="C51" s="134">
         <v>44727</v>
       </c>
-      <c r="D51" s="146" t="s">
+      <c r="D51" s="133" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="146">
+      <c r="A52" s="133">
         <v>11760</v>
       </c>
-      <c r="B52" s="146" t="s">
+      <c r="B52" s="133" t="s">
         <v>662</v>
       </c>
-      <c r="C52" s="147">
+      <c r="C52" s="134">
         <v>44693</v>
       </c>
-      <c r="D52" s="146" t="s">
+      <c r="D52" s="133" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="146">
+      <c r="A53" s="133">
         <v>11807</v>
       </c>
-      <c r="B53" s="146" t="s">
+      <c r="B53" s="133" t="s">
         <v>663</v>
       </c>
-      <c r="C53" s="147">
+      <c r="C53" s="134">
         <v>44764</v>
       </c>
-      <c r="D53" s="146" t="s">
+      <c r="D53" s="133" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="146">
+      <c r="A54" s="133">
         <v>11813</v>
       </c>
-      <c r="B54" s="146" t="s">
+      <c r="B54" s="133" t="s">
         <v>664</v>
       </c>
-      <c r="C54" s="147">
+      <c r="C54" s="134">
         <v>44786</v>
       </c>
-      <c r="D54" s="146" t="s">
+      <c r="D54" s="133" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="146">
+      <c r="A55" s="133">
         <v>11823</v>
       </c>
-      <c r="B55" s="146" t="s">
+      <c r="B55" s="133" t="s">
         <v>665</v>
       </c>
-      <c r="C55" s="147">
+      <c r="C55" s="134">
         <v>44854</v>
       </c>
-      <c r="D55" s="146" t="s">
+      <c r="D55" s="133" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="146">
+      <c r="A56" s="133">
         <v>11828</v>
       </c>
-      <c r="B56" s="146" t="s">
+      <c r="B56" s="133" t="s">
         <v>666</v>
       </c>
-      <c r="C56" s="147">
+      <c r="C56" s="134">
         <v>44810</v>
       </c>
-      <c r="D56" s="146" t="s">
+      <c r="D56" s="133" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="146">
+      <c r="A57" s="133">
         <v>11836</v>
       </c>
-      <c r="B57" s="146" t="s">
+      <c r="B57" s="133" t="s">
         <v>667</v>
       </c>
-      <c r="C57" s="147">
+      <c r="C57" s="134">
         <v>44834</v>
       </c>
-      <c r="D57" s="146" t="s">
+      <c r="D57" s="133" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="146">
+      <c r="A58" s="133">
         <v>11839</v>
       </c>
-      <c r="B58" s="146" t="s">
+      <c r="B58" s="133" t="s">
         <v>668</v>
       </c>
-      <c r="C58" s="147">
+      <c r="C58" s="134">
         <v>44820</v>
       </c>
-      <c r="D58" s="146" t="s">
+      <c r="D58" s="133" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="146">
+      <c r="A59" s="133">
         <v>11843</v>
       </c>
-      <c r="B59" s="146" t="s">
+      <c r="B59" s="133" t="s">
         <v>669</v>
       </c>
-      <c r="C59" s="147">
+      <c r="C59" s="134">
         <v>44835</v>
       </c>
-      <c r="D59" s="146" t="s">
+      <c r="D59" s="133" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="146">
+      <c r="A60" s="133">
         <v>11854</v>
       </c>
-      <c r="B60" s="146" t="s">
+      <c r="B60" s="133" t="s">
         <v>670</v>
       </c>
-      <c r="C60" s="147">
+      <c r="C60" s="134">
         <v>44869</v>
       </c>
-      <c r="D60" s="146" t="s">
+      <c r="D60" s="133" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="146">
+      <c r="A61" s="133">
         <v>11861</v>
       </c>
-      <c r="B61" s="146" t="s">
+      <c r="B61" s="133" t="s">
         <v>671</v>
       </c>
-      <c r="C61" s="147">
+      <c r="C61" s="134">
         <v>44849</v>
       </c>
-      <c r="D61" s="146" t="s">
+      <c r="D61" s="133" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="146">
+      <c r="A62" s="133">
         <v>11875</v>
       </c>
-      <c r="B62" s="146" t="s">
+      <c r="B62" s="133" t="s">
         <v>672</v>
       </c>
-      <c r="C62" s="147">
+      <c r="C62" s="134">
         <v>44861</v>
       </c>
-      <c r="D62" s="146" t="s">
+      <c r="D62" s="133" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="146">
+      <c r="A63" s="133">
         <v>11877</v>
       </c>
-      <c r="B63" s="146" t="s">
+      <c r="B63" s="133" t="s">
         <v>673</v>
       </c>
-      <c r="C63" s="147">
+      <c r="C63" s="134">
         <v>44928</v>
       </c>
-      <c r="D63" s="146" t="s">
+      <c r="D63" s="133" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="146">
+      <c r="A64" s="133">
         <v>11898</v>
       </c>
-      <c r="B64" s="146" t="s">
+      <c r="B64" s="133" t="s">
         <v>674</v>
       </c>
-      <c r="C64" s="147">
+      <c r="C64" s="134">
         <v>44905</v>
       </c>
-      <c r="D64" s="146" t="s">
+      <c r="D64" s="133" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="146">
+      <c r="A65" s="133">
         <v>11900</v>
       </c>
-      <c r="B65" s="146" t="s">
+      <c r="B65" s="133" t="s">
         <v>675</v>
       </c>
-      <c r="C65" s="147">
+      <c r="C65" s="134">
         <v>44965</v>
       </c>
-      <c r="D65" s="146" t="s">
+      <c r="D65" s="133" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="146">
+      <c r="A66" s="133">
         <v>11906</v>
       </c>
-      <c r="B66" s="146" t="s">
+      <c r="B66" s="133" t="s">
         <v>676</v>
       </c>
-      <c r="C66" s="147">
+      <c r="C66" s="134">
         <v>44912</v>
       </c>
-      <c r="D66" s="146" t="s">
+      <c r="D66" s="133" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="146">
+      <c r="A67" s="133">
         <v>11985</v>
       </c>
-      <c r="B67" s="146" t="s">
+      <c r="B67" s="133" t="s">
         <v>677</v>
       </c>
-      <c r="C67" s="147">
+      <c r="C67" s="134">
         <v>45086</v>
       </c>
-      <c r="D67" s="146" t="s">
+      <c r="D67" s="133" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="146">
+      <c r="A68" s="133">
         <v>11989</v>
       </c>
-      <c r="B68" s="146" t="s">
+      <c r="B68" s="133" t="s">
         <v>678</v>
       </c>
-      <c r="C68" s="147">
+      <c r="C68" s="134">
         <v>45057</v>
       </c>
-      <c r="D68" s="146" t="s">
+      <c r="D68" s="133" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="146">
+      <c r="A69" s="133">
         <v>11990</v>
       </c>
-      <c r="B69" s="146" t="s">
+      <c r="B69" s="133" t="s">
         <v>679</v>
       </c>
-      <c r="C69" s="147">
+      <c r="C69" s="134">
         <v>45085</v>
       </c>
-      <c r="D69" s="146" t="s">
+      <c r="D69" s="133" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="146">
+      <c r="A70" s="133">
         <v>11996</v>
       </c>
-      <c r="B70" s="146" t="s">
+      <c r="B70" s="133" t="s">
         <v>680</v>
       </c>
-      <c r="C70" s="147">
+      <c r="C70" s="134">
         <v>45078</v>
       </c>
-      <c r="D70" s="146" t="s">
+      <c r="D70" s="133" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="146">
+      <c r="A71" s="133">
         <v>13020</v>
       </c>
-      <c r="B71" s="146" t="s">
+      <c r="B71" s="133" t="s">
         <v>681</v>
       </c>
-      <c r="C71" s="147">
+      <c r="C71" s="134">
         <v>45150</v>
       </c>
-      <c r="D71" s="146" t="s">
+      <c r="D71" s="133" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="146">
+      <c r="A72" s="133">
         <v>13058</v>
       </c>
-      <c r="B72" s="146" t="s">
+      <c r="B72" s="133" t="s">
         <v>682</v>
       </c>
-      <c r="C72" s="147">
+      <c r="C72" s="134">
         <v>45262</v>
       </c>
-      <c r="D72" s="146" t="s">
+      <c r="D72" s="133" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="146">
+      <c r="A73" s="133">
         <v>13070</v>
       </c>
-      <c r="B73" s="146" t="s">
+      <c r="B73" s="133" t="s">
         <v>683</v>
       </c>
-      <c r="C73" s="147">
+      <c r="C73" s="134">
         <v>45278</v>
       </c>
-      <c r="D73" s="146" t="s">
+      <c r="D73" s="133" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="146">
+      <c r="A74" s="133">
         <v>13088</v>
       </c>
-      <c r="B74" s="146" t="s">
+      <c r="B74" s="133" t="s">
         <v>684</v>
       </c>
-      <c r="C74" s="147">
+      <c r="C74" s="134">
         <v>45413</v>
       </c>
-      <c r="D74" s="146" t="s">
+      <c r="D74" s="133" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="146">
+      <c r="A75" s="133">
         <v>13173</v>
       </c>
-      <c r="B75" s="146" t="s">
+      <c r="B75" s="133" t="s">
         <v>685</v>
       </c>
-      <c r="C75" s="147">
+      <c r="C75" s="134">
         <v>45765</v>
       </c>
-      <c r="D75" s="146" t="s">
+      <c r="D75" s="133" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="146">
+      <c r="A76" s="133">
         <v>13180</v>
       </c>
-      <c r="B76" s="146" t="s">
+      <c r="B76" s="133" t="s">
         <v>686</v>
       </c>
-      <c r="C76" s="147">
+      <c r="C76" s="134">
         <v>45892</v>
       </c>
-      <c r="D76" s="146" t="s">
+      <c r="D76" s="133" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="146">
+      <c r="A77" s="133">
         <v>13187</v>
       </c>
-      <c r="B77" s="146" t="s">
+      <c r="B77" s="133" t="s">
         <v>687</v>
       </c>
-      <c r="C77" s="147">
+      <c r="C77" s="134">
         <v>46003</v>
       </c>
-      <c r="D77" s="146" t="s">
+      <c r="D77" s="133" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="148">
+      <c r="A78" s="135">
         <v>13199</v>
       </c>
-      <c r="C78" s="147">
+      <c r="C78" s="134">
         <v>46284</v>
       </c>
-      <c r="D78" s="146" t="s">
+      <c r="D78" s="133" t="s">
         <v>590</v>
       </c>
     </row>

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Максим\Yandex.Disk\Магазины\паспорт магазина\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Project\Passport_Sibir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8745B52A-EA2F-4B04-BA33-70AB38F3CAA8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69417D47-0774-4FB5-A7D9-19BC1F1A9A6E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3260,30 +3260,6 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3297,6 +3273,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3652,108 +3652,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="148" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="138" t="s">
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="143" t="s">
         <v>229</v>
       </c>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="138" t="s">
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="143" t="s">
         <v>230</v>
       </c>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="143" t="s">
+      <c r="X1" s="146"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="145"/>
+      <c r="AC1" s="149" t="s">
         <v>231</v>
       </c>
       <c r="AD1" s="144"/>
-      <c r="AE1" s="145"/>
+      <c r="AE1" s="150"/>
       <c r="AF1" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="AG1" s="138" t="s">
+      <c r="AG1" s="143" t="s">
         <v>233</v>
       </c>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="138" t="s">
+      <c r="AH1" s="145"/>
+      <c r="AI1" s="143" t="s">
         <v>234</v>
       </c>
       <c r="AJ1" s="144"/>
-      <c r="AK1" s="140"/>
-      <c r="AL1" s="138" t="s">
+      <c r="AK1" s="145"/>
+      <c r="AL1" s="143" t="s">
         <v>235</v>
       </c>
-      <c r="AM1" s="140"/>
-      <c r="AN1" s="138" t="s">
+      <c r="AM1" s="145"/>
+      <c r="AN1" s="143" t="s">
         <v>236</v>
       </c>
-      <c r="AO1" s="139"/>
-      <c r="AP1" s="140"/>
+      <c r="AO1" s="146"/>
+      <c r="AP1" s="145"/>
       <c r="AQ1" s="65" t="s">
         <v>237</v>
       </c>
       <c r="AR1" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="AS1" s="146" t="s">
+      <c r="AS1" s="138" t="s">
         <v>239</v>
       </c>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="148"/>
-      <c r="AV1" s="149" t="s">
+      <c r="AT1" s="139"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="141" t="s">
         <v>240</v>
       </c>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="148"/>
-      <c r="BA1" s="138" t="s">
+      <c r="AW1" s="139"/>
+      <c r="AX1" s="139"/>
+      <c r="AY1" s="139"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="143" t="s">
         <v>406</v>
       </c>
-      <c r="BB1" s="138"/>
-      <c r="BC1" s="138"/>
-      <c r="BD1" s="138"/>
-      <c r="BE1" s="139"/>
-      <c r="BF1" s="139"/>
-      <c r="BG1" s="139"/>
-      <c r="BH1" s="140"/>
-      <c r="BI1" s="149" t="s">
+      <c r="BB1" s="143"/>
+      <c r="BC1" s="143"/>
+      <c r="BD1" s="143"/>
+      <c r="BE1" s="146"/>
+      <c r="BF1" s="146"/>
+      <c r="BG1" s="146"/>
+      <c r="BH1" s="145"/>
+      <c r="BI1" s="141" t="s">
         <v>241</v>
       </c>
-      <c r="BJ1" s="147"/>
-      <c r="BK1" s="147"/>
-      <c r="BL1" s="147"/>
-      <c r="BM1" s="147"/>
-      <c r="BN1" s="150"/>
-      <c r="BO1" s="146" t="s">
+      <c r="BJ1" s="139"/>
+      <c r="BK1" s="139"/>
+      <c r="BL1" s="139"/>
+      <c r="BM1" s="139"/>
+      <c r="BN1" s="142"/>
+      <c r="BO1" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="BP1" s="147"/>
-      <c r="BQ1" s="147"/>
-      <c r="BR1" s="148"/>
+      <c r="BP1" s="139"/>
+      <c r="BQ1" s="139"/>
+      <c r="BR1" s="140"/>
       <c r="BS1" s="11"/>
     </row>
     <row r="2" spans="1:71" ht="61.8" thickBot="1">
@@ -15076,13 +15076,13 @@
         <v>18</v>
       </c>
       <c r="AN57" s="64" t="s">
-        <v>96</v>
-      </c>
-      <c r="AO57" s="15">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="AO57" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="AP57" s="23" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="AQ57" s="49" t="s">
         <v>23</v>
@@ -16296,13 +16296,13 @@
         <v>23</v>
       </c>
       <c r="AN63" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AO63" s="15" t="s">
-        <v>23</v>
+        <v>96</v>
+      </c>
+      <c r="AO63" s="15">
+        <v>1</v>
       </c>
       <c r="AP63" s="23" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="AQ63" s="49" t="s">
         <v>23</v>
@@ -19915,6 +19915,11 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="13">
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="BO1:BR1"/>
     <mergeCell ref="BI1:BN1"/>
     <mergeCell ref="AI1:AK1"/>
@@ -19923,11 +19928,6 @@
     <mergeCell ref="BA1:BH1"/>
     <mergeCell ref="AV1:AZ1"/>
     <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="AC1:AE1"/>
   </mergeCells>
   <conditionalFormatting sqref="V4 BM4 BL5 BN6 BM7 V8 BJ8 U9 BI9 BL10:BL14 V14 BN15 V17 BI19 BL20 BM21 V22 BL22 BI23 BJ24 V24:V25 BN25 BL26:BL27 BM28 BJ29 V29:V30 BI30 V33 BK33 BL34:BL36 V35 U36 V37 BM37 V39 BN41 BN52 BL53:BL55 U56 BN56 V57 V61 BJ61 V70 V72 U76 BK76 BI77:BI78 BL16:BL18 BL63:BL75 BL57:BL60 BL38:BL40 BJ79 BL42:BL51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Project\Passport_Sibir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69417D47-0774-4FB5-A7D9-19BC1F1A9A6E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60193D4F-DDCD-4F88-BB75-AADBA0CAA802}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3260,6 +3260,30 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3273,30 +3297,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3652,108 +3652,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="142" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="143" t="s">
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="138" t="s">
         <v>229</v>
       </c>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="143" t="s">
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="138" t="s">
         <v>230</v>
       </c>
-      <c r="X1" s="146"/>
-      <c r="Y1" s="146"/>
-      <c r="Z1" s="147"/>
-      <c r="AA1" s="147"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="149" t="s">
+      <c r="X1" s="139"/>
+      <c r="Y1" s="139"/>
+      <c r="Z1" s="141"/>
+      <c r="AA1" s="141"/>
+      <c r="AB1" s="140"/>
+      <c r="AC1" s="143" t="s">
         <v>231</v>
       </c>
       <c r="AD1" s="144"/>
-      <c r="AE1" s="150"/>
+      <c r="AE1" s="145"/>
       <c r="AF1" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="AG1" s="143" t="s">
+      <c r="AG1" s="138" t="s">
         <v>233</v>
       </c>
-      <c r="AH1" s="145"/>
-      <c r="AI1" s="143" t="s">
+      <c r="AH1" s="140"/>
+      <c r="AI1" s="138" t="s">
         <v>234</v>
       </c>
       <c r="AJ1" s="144"/>
-      <c r="AK1" s="145"/>
-      <c r="AL1" s="143" t="s">
+      <c r="AK1" s="140"/>
+      <c r="AL1" s="138" t="s">
         <v>235</v>
       </c>
-      <c r="AM1" s="145"/>
-      <c r="AN1" s="143" t="s">
+      <c r="AM1" s="140"/>
+      <c r="AN1" s="138" t="s">
         <v>236</v>
       </c>
-      <c r="AO1" s="146"/>
-      <c r="AP1" s="145"/>
+      <c r="AO1" s="139"/>
+      <c r="AP1" s="140"/>
       <c r="AQ1" s="65" t="s">
         <v>237</v>
       </c>
       <c r="AR1" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="AS1" s="138" t="s">
+      <c r="AS1" s="146" t="s">
         <v>239</v>
       </c>
-      <c r="AT1" s="139"/>
-      <c r="AU1" s="140"/>
-      <c r="AV1" s="141" t="s">
+      <c r="AT1" s="147"/>
+      <c r="AU1" s="148"/>
+      <c r="AV1" s="149" t="s">
         <v>240</v>
       </c>
-      <c r="AW1" s="139"/>
-      <c r="AX1" s="139"/>
-      <c r="AY1" s="139"/>
-      <c r="AZ1" s="140"/>
-      <c r="BA1" s="143" t="s">
+      <c r="AW1" s="147"/>
+      <c r="AX1" s="147"/>
+      <c r="AY1" s="147"/>
+      <c r="AZ1" s="148"/>
+      <c r="BA1" s="138" t="s">
         <v>406</v>
       </c>
-      <c r="BB1" s="143"/>
-      <c r="BC1" s="143"/>
-      <c r="BD1" s="143"/>
-      <c r="BE1" s="146"/>
-      <c r="BF1" s="146"/>
-      <c r="BG1" s="146"/>
-      <c r="BH1" s="145"/>
-      <c r="BI1" s="141" t="s">
+      <c r="BB1" s="138"/>
+      <c r="BC1" s="138"/>
+      <c r="BD1" s="138"/>
+      <c r="BE1" s="139"/>
+      <c r="BF1" s="139"/>
+      <c r="BG1" s="139"/>
+      <c r="BH1" s="140"/>
+      <c r="BI1" s="149" t="s">
         <v>241</v>
       </c>
-      <c r="BJ1" s="139"/>
-      <c r="BK1" s="139"/>
-      <c r="BL1" s="139"/>
-      <c r="BM1" s="139"/>
-      <c r="BN1" s="142"/>
-      <c r="BO1" s="138" t="s">
+      <c r="BJ1" s="147"/>
+      <c r="BK1" s="147"/>
+      <c r="BL1" s="147"/>
+      <c r="BM1" s="147"/>
+      <c r="BN1" s="150"/>
+      <c r="BO1" s="146" t="s">
         <v>607</v>
       </c>
-      <c r="BP1" s="139"/>
-      <c r="BQ1" s="139"/>
-      <c r="BR1" s="140"/>
+      <c r="BP1" s="147"/>
+      <c r="BQ1" s="147"/>
+      <c r="BR1" s="148"/>
       <c r="BS1" s="11"/>
     </row>
     <row r="2" spans="1:71" ht="61.8" thickBot="1">
@@ -5322,7 +5322,9 @@
       <c r="AR9" s="114">
         <v>3</v>
       </c>
-      <c r="AS9" s="7"/>
+      <c r="AS9" s="7">
+        <v>1</v>
+      </c>
       <c r="AT9" s="2" t="s">
         <v>96</v>
       </c>
@@ -15887,7 +15889,7 @@
         <v>96</v>
       </c>
       <c r="AM61" s="24">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AN61" s="64" t="s">
         <v>96</v>
@@ -19915,11 +19917,6 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="13">
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="BO1:BR1"/>
     <mergeCell ref="BI1:BN1"/>
     <mergeCell ref="AI1:AK1"/>
@@ -19928,6 +19925,11 @@
     <mergeCell ref="BA1:BH1"/>
     <mergeCell ref="AV1:AZ1"/>
     <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="AC1:AE1"/>
   </mergeCells>
   <conditionalFormatting sqref="V4 BM4 BL5 BN6 BM7 V8 BJ8 U9 BI9 BL10:BL14 V14 BN15 V17 BI19 BL20 BM21 V22 BL22 BI23 BJ24 V24:V25 BN25 BL26:BL27 BM28 BJ29 V29:V30 BI30 V33 BK33 BL34:BL36 V35 U36 V37 BM37 V39 BN41 BN52 BL53:BL55 U56 BN56 V57 V61 BJ61 V70 V72 U76 BK76 BI77:BI78 BL16:BL18 BL63:BL75 BL57:BL60 BL38:BL40 BJ79 BL42:BL51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">

--- a/паспорт магазина.xlsx
+++ b/паспорт магазина.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Project\Passport_Sibir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60193D4F-DDCD-4F88-BB75-AADBA0CAA802}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113C7514-AB00-451C-AFD4-4D8B499956AF}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="504" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3260,30 +3260,6 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3297,6 +3273,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3652,108 +3652,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="60.45" customHeight="1" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="148" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="138" t="s">
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="143" t="s">
         <v>229</v>
       </c>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="138" t="s">
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="143" t="s">
         <v>230</v>
       </c>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="143" t="s">
+      <c r="X1" s="146"/>
+      <c r="Y1" s="146"/>
+      <c r="Z1" s="147"/>
+      <c r="AA1" s="147"/>
+      <c r="AB1" s="145"/>
+      <c r="AC1" s="149" t="s">
         <v>231</v>
       </c>
       <c r="AD1" s="144"/>
-      <c r="AE1" s="145"/>
+      <c r="AE1" s="150"/>
       <c r="AF1" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="AG1" s="138" t="s">
+      <c r="AG1" s="143" t="s">
         <v>233</v>
       </c>
-      <c r="AH1" s="140"/>
-      <c r="AI1" s="138" t="s">
+      <c r="AH1" s="145"/>
+      <c r="AI1" s="143" t="s">
         <v>234</v>
       </c>
       <c r="AJ1" s="144"/>
-      <c r="AK1" s="140"/>
-      <c r="AL1" s="138" t="s">
+      <c r="AK1" s="145"/>
+      <c r="AL1" s="143" t="s">
         <v>235</v>
       </c>
-      <c r="AM1" s="140"/>
-      <c r="AN1" s="138" t="s">
+      <c r="AM1" s="145"/>
+      <c r="AN1" s="143" t="s">
         <v>236</v>
       </c>
-      <c r="AO1" s="139"/>
-      <c r="AP1" s="140"/>
+      <c r="AO1" s="146"/>
+      <c r="AP1" s="145"/>
       <c r="AQ1" s="65" t="s">
         <v>237</v>
       </c>
       <c r="AR1" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="AS1" s="146" t="s">
+      <c r="AS1" s="138" t="s">
         <v>239</v>
       </c>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="148"/>
-      <c r="AV1" s="149" t="s">
+      <c r="AT1" s="139"/>
+      <c r="AU1" s="140"/>
+      <c r="AV1" s="141" t="s">
         <v>240</v>
       </c>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="148"/>
-      <c r="BA1" s="138" t="s">
+      <c r="AW1" s="139"/>
+      <c r="AX1" s="139"/>
+      <c r="AY1" s="139"/>
+      <c r="AZ1" s="140"/>
+      <c r="BA1" s="143" t="s">
         <v>406</v>
       </c>
-      <c r="BB1" s="138"/>
-      <c r="BC1" s="138"/>
-      <c r="BD1" s="138"/>
-      <c r="BE1" s="139"/>
-      <c r="BF1" s="139"/>
-      <c r="BG1" s="139"/>
-      <c r="BH1" s="140"/>
-      <c r="BI1" s="149" t="s">
+      <c r="BB1" s="143"/>
+      <c r="BC1" s="143"/>
+      <c r="BD1" s="143"/>
+      <c r="BE1" s="146"/>
+      <c r="BF1" s="146"/>
+      <c r="BG1" s="146"/>
+      <c r="BH1" s="145"/>
+      <c r="BI1" s="141" t="s">
         <v>241</v>
       </c>
-      <c r="BJ1" s="147"/>
-      <c r="BK1" s="147"/>
-      <c r="BL1" s="147"/>
-      <c r="BM1" s="147"/>
-      <c r="BN1" s="150"/>
-      <c r="BO1" s="146" t="s">
+      <c r="BJ1" s="139"/>
+      <c r="BK1" s="139"/>
+      <c r="BL1" s="139"/>
+      <c r="BM1" s="139"/>
+      <c r="BN1" s="142"/>
+      <c r="BO1" s="138" t="s">
         <v>607</v>
       </c>
-      <c r="BP1" s="147"/>
-      <c r="BQ1" s="147"/>
-      <c r="BR1" s="148"/>
+      <c r="BP1" s="139"/>
+      <c r="BQ1" s="139"/>
+      <c r="BR1" s="140"/>
       <c r="BS1" s="11"/>
     </row>
     <row r="2" spans="1:71" ht="61.8" thickBot="1">
@@ -18739,10 +18739,10 @@
         <v>96</v>
       </c>
       <c r="AO75" s="15">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AP75" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AQ75" s="49" t="s">
         <v>23</v>
@@ -19917,6 +19917,11 @@
     <sortCondition ref="C3:C78"/>
   </sortState>
   <mergeCells count="13">
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="AC1:AE1"/>
     <mergeCell ref="BO1:BR1"/>
     <mergeCell ref="BI1:BN1"/>
     <mergeCell ref="AI1:AK1"/>
@@ -19925,11 +19930,6 @@
     <mergeCell ref="BA1:BH1"/>
     <mergeCell ref="AV1:AZ1"/>
     <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="AC1:AE1"/>
   </mergeCells>
   <conditionalFormatting sqref="V4 BM4 BL5 BN6 BM7 V8 BJ8 U9 BI9 BL10:BL14 V14 BN15 V17 BI19 BL20 BM21 V22 BL22 BI23 BJ24 V24:V25 BN25 BL26:BL27 BM28 BJ29 V29:V30 BI30 V33 BK33 BL34:BL36 V35 U36 V37 BM37 V39 BN41 BN52 BL53:BL55 U56 BN56 V57 V61 BJ61 V70 V72 U76 BK76 BI77:BI78 BL16:BL18 BL63:BL75 BL57:BL60 BL38:BL40 BJ79 BL42:BL51">
     <cfRule type="containsBlanks" dxfId="2" priority="8">
